--- a/光伏配储项目/电价数据/2026/湾琴站.xlsx
+++ b/光伏配储项目/电价数据/2026/湾琴站.xlsx
@@ -16,10 +16,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="3">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
-    <numFmt numFmtId="166" formatCode="yyyy/mm/dd"/>
   </numFmts>
   <fonts count="2">
     <font>
@@ -64,7 +63,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -430,13 +429,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CS116"/>
+  <dimension ref="A1:CS143"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>日期</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
@@ -34613,6 +34612,7917 @@
       </c>
       <c r="CS116" t="n">
         <v>0.50997</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="2" t="n">
+        <v>46138</v>
+      </c>
+      <c r="B117" t="n">
+        <v>0.38047</v>
+      </c>
+      <c r="C117" t="n">
+        <v>0.5314500000000001</v>
+      </c>
+      <c r="D117" t="n">
+        <v>0.5436</v>
+      </c>
+      <c r="E117" t="n">
+        <v>0.30414</v>
+      </c>
+      <c r="F117" t="n">
+        <v>0.31472</v>
+      </c>
+      <c r="G117" t="n">
+        <v>0.30523</v>
+      </c>
+      <c r="H117" t="n">
+        <v>0.43856</v>
+      </c>
+      <c r="I117" t="n">
+        <v>0.45537</v>
+      </c>
+      <c r="J117" t="n">
+        <v>0.44025</v>
+      </c>
+      <c r="K117" t="n">
+        <v>0.42365</v>
+      </c>
+      <c r="L117" t="n">
+        <v>0.42008</v>
+      </c>
+      <c r="M117" t="n">
+        <v>0.40925</v>
+      </c>
+      <c r="N117" t="n">
+        <v>0.39929</v>
+      </c>
+      <c r="O117" t="n">
+        <v>0.40122</v>
+      </c>
+      <c r="P117" t="n">
+        <v>0.38603</v>
+      </c>
+      <c r="Q117" t="n">
+        <v>0.40253</v>
+      </c>
+      <c r="R117" t="n">
+        <v>0.42412</v>
+      </c>
+      <c r="S117" t="n">
+        <v>0.41363</v>
+      </c>
+      <c r="T117" t="n">
+        <v>0.35571</v>
+      </c>
+      <c r="U117" t="n">
+        <v>0.39257</v>
+      </c>
+      <c r="V117" t="n">
+        <v>0.38548</v>
+      </c>
+      <c r="W117" t="n">
+        <v>0.41802</v>
+      </c>
+      <c r="X117" t="n">
+        <v>0.39205</v>
+      </c>
+      <c r="Y117" t="n">
+        <v>0.42103</v>
+      </c>
+      <c r="Z117" t="n">
+        <v>0.41499</v>
+      </c>
+      <c r="AA117" t="n">
+        <v>0.42497</v>
+      </c>
+      <c r="AB117" t="n">
+        <v>0.41349</v>
+      </c>
+      <c r="AC117" t="n">
+        <v>0.44506</v>
+      </c>
+      <c r="AD117" t="n">
+        <v>0.3593</v>
+      </c>
+      <c r="AE117" t="n">
+        <v>0.29984</v>
+      </c>
+      <c r="AF117" t="n">
+        <v>0.33298</v>
+      </c>
+      <c r="AG117" t="n">
+        <v>0.30828</v>
+      </c>
+      <c r="AH117" t="n">
+        <v>0.25227</v>
+      </c>
+      <c r="AI117" t="n">
+        <v>0.29473</v>
+      </c>
+      <c r="AJ117" t="n">
+        <v>0.28259</v>
+      </c>
+      <c r="AK117" t="n">
+        <v>-0.01486</v>
+      </c>
+      <c r="AL117" t="n">
+        <v>0.11318</v>
+      </c>
+      <c r="AM117" t="n">
+        <v>-0.03168</v>
+      </c>
+      <c r="AN117" t="n">
+        <v>-0.02382</v>
+      </c>
+      <c r="AO117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AP117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AQ117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AR117" t="n">
+        <v>0.03706</v>
+      </c>
+      <c r="AS117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AT117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AU117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AV117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AW117" t="n">
+        <v>0.08322</v>
+      </c>
+      <c r="AX117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AZ117" t="n">
+        <v>0.00624</v>
+      </c>
+      <c r="BA117" t="n">
+        <v>0.14475</v>
+      </c>
+      <c r="BB117" t="n">
+        <v>0.21188</v>
+      </c>
+      <c r="BC117" t="n">
+        <v>0.2394</v>
+      </c>
+      <c r="BD117" t="n">
+        <v>0.15079</v>
+      </c>
+      <c r="BE117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BF117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BG117" t="n">
+        <v>-0.01325</v>
+      </c>
+      <c r="BH117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BI117" t="n">
+        <v>0.11925</v>
+      </c>
+      <c r="BJ117" t="n">
+        <v>-0.01367</v>
+      </c>
+      <c r="BK117" t="n">
+        <v>0.09248000000000001</v>
+      </c>
+      <c r="BL117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BM117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BN117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BO117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BP117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BQ117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BR117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BS117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BT117" t="n">
+        <v>0.25213</v>
+      </c>
+      <c r="BU117" t="n">
+        <v>0.07528</v>
+      </c>
+      <c r="BV117" t="n">
+        <v>0.18379</v>
+      </c>
+      <c r="BW117" t="n">
+        <v>0.4288</v>
+      </c>
+      <c r="BX117" t="n">
+        <v>0.17836</v>
+      </c>
+      <c r="BY117" t="n">
+        <v>0.44519</v>
+      </c>
+      <c r="BZ117" t="n">
+        <v>0.07016</v>
+      </c>
+      <c r="CA117" t="n">
+        <v>0.24516</v>
+      </c>
+      <c r="CB117" t="n">
+        <v>0.5630700000000001</v>
+      </c>
+      <c r="CC117" t="n">
+        <v>0.60722</v>
+      </c>
+      <c r="CD117" t="n">
+        <v>0.22125</v>
+      </c>
+      <c r="CE117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CF117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CG117" t="n">
+        <v>0.2852</v>
+      </c>
+      <c r="CH117" t="n">
+        <v>0.29045</v>
+      </c>
+      <c r="CI117" t="n">
+        <v>0.37961</v>
+      </c>
+      <c r="CJ117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CK117" t="n">
+        <v>0.29106</v>
+      </c>
+      <c r="CL117" t="n">
+        <v>0.32504</v>
+      </c>
+      <c r="CM117" t="n">
+        <v>0.41476</v>
+      </c>
+      <c r="CN117" t="n">
+        <v>0.35297</v>
+      </c>
+      <c r="CO117" t="n">
+        <v>0.32698</v>
+      </c>
+      <c r="CP117" t="n">
+        <v>0.47877</v>
+      </c>
+      <c r="CQ117" t="n">
+        <v>0.4003</v>
+      </c>
+      <c r="CR117" t="n">
+        <v>0.41181</v>
+      </c>
+      <c r="CS117" t="n">
+        <v>0.42091</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="2" t="n">
+        <v>46139</v>
+      </c>
+      <c r="B118" t="n">
+        <v>0.32999</v>
+      </c>
+      <c r="C118" t="n">
+        <v>0.43803</v>
+      </c>
+      <c r="D118" t="n">
+        <v>1.15094</v>
+      </c>
+      <c r="E118" t="n">
+        <v>0.6921799999999999</v>
+      </c>
+      <c r="F118" t="n">
+        <v>0.30396</v>
+      </c>
+      <c r="G118" t="n">
+        <v>0.79465</v>
+      </c>
+      <c r="H118" t="n">
+        <v>0.5365800000000001</v>
+      </c>
+      <c r="I118" t="n">
+        <v>0.52297</v>
+      </c>
+      <c r="J118" t="n">
+        <v>0.50636</v>
+      </c>
+      <c r="K118" t="n">
+        <v>0.46432</v>
+      </c>
+      <c r="L118" t="n">
+        <v>0.50002</v>
+      </c>
+      <c r="M118" t="n">
+        <v>0.37353</v>
+      </c>
+      <c r="N118" t="n">
+        <v>0.4738</v>
+      </c>
+      <c r="O118" t="n">
+        <v>0.35512</v>
+      </c>
+      <c r="P118" t="n">
+        <v>0.38098</v>
+      </c>
+      <c r="Q118" t="n">
+        <v>0.39215</v>
+      </c>
+      <c r="R118" t="n">
+        <v>0.3377</v>
+      </c>
+      <c r="S118" t="n">
+        <v>0.37167</v>
+      </c>
+      <c r="T118" t="n">
+        <v>0.35726</v>
+      </c>
+      <c r="U118" t="n">
+        <v>0.36063</v>
+      </c>
+      <c r="V118" t="n">
+        <v>0.3766</v>
+      </c>
+      <c r="W118" t="n">
+        <v>0.37656</v>
+      </c>
+      <c r="X118" t="n">
+        <v>0.36057</v>
+      </c>
+      <c r="Y118" t="n">
+        <v>0.38148</v>
+      </c>
+      <c r="Z118" t="n">
+        <v>0.42254</v>
+      </c>
+      <c r="AA118" t="n">
+        <v>0.51373</v>
+      </c>
+      <c r="AB118" t="n">
+        <v>0.6238400000000001</v>
+      </c>
+      <c r="AC118" t="n">
+        <v>0.7251599999999999</v>
+      </c>
+      <c r="AD118" t="n">
+        <v>0.43607</v>
+      </c>
+      <c r="AE118" t="n">
+        <v>0.32132</v>
+      </c>
+      <c r="AF118" t="n">
+        <v>0.31797</v>
+      </c>
+      <c r="AG118" t="n">
+        <v>0.3462</v>
+      </c>
+      <c r="AH118" t="n">
+        <v>0.32349</v>
+      </c>
+      <c r="AI118" t="n">
+        <v>0.12841</v>
+      </c>
+      <c r="AJ118" t="n">
+        <v>0.28912</v>
+      </c>
+      <c r="AK118" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AL118" t="n">
+        <v>0.30266</v>
+      </c>
+      <c r="AM118" t="n">
+        <v>0.16478</v>
+      </c>
+      <c r="AN118" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AO118" t="n">
+        <v>0.12231</v>
+      </c>
+      <c r="AP118" t="n">
+        <v>0.25709</v>
+      </c>
+      <c r="AQ118" t="n">
+        <v>0.19418</v>
+      </c>
+      <c r="AR118" t="n">
+        <v>0.14744</v>
+      </c>
+      <c r="AS118" t="n">
+        <v>0.30867</v>
+      </c>
+      <c r="AT118" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AU118" t="n">
+        <v>0.12411</v>
+      </c>
+      <c r="AV118" t="n">
+        <v>0.29444</v>
+      </c>
+      <c r="AW118" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AX118" t="n">
+        <v>0.16144</v>
+      </c>
+      <c r="AY118" t="n">
+        <v>-0.00329</v>
+      </c>
+      <c r="AZ118" t="n">
+        <v>0.05783</v>
+      </c>
+      <c r="BA118" t="n">
+        <v>0.11731</v>
+      </c>
+      <c r="BB118" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BC118" t="n">
+        <v>0.2746</v>
+      </c>
+      <c r="BD118" t="n">
+        <v>0.14097</v>
+      </c>
+      <c r="BE118" t="n">
+        <v>0.34101</v>
+      </c>
+      <c r="BF118" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BG118" t="n">
+        <v>0.25514</v>
+      </c>
+      <c r="BH118" t="n">
+        <v>0.30409</v>
+      </c>
+      <c r="BI118" t="n">
+        <v>0.20926</v>
+      </c>
+      <c r="BJ118" t="n">
+        <v>0.27572</v>
+      </c>
+      <c r="BK118" t="n">
+        <v>0.29563</v>
+      </c>
+      <c r="BL118" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BM118" t="n">
+        <v>-0.00437</v>
+      </c>
+      <c r="BN118" t="n">
+        <v>-0.04422</v>
+      </c>
+      <c r="BO118" t="n">
+        <v>0.03016</v>
+      </c>
+      <c r="BP118" t="n">
+        <v>-0.01574</v>
+      </c>
+      <c r="BQ118" t="n">
+        <v>0.23141</v>
+      </c>
+      <c r="BR118" t="n">
+        <v>0.25285</v>
+      </c>
+      <c r="BS118" t="n">
+        <v>0.36089</v>
+      </c>
+      <c r="BT118" t="n">
+        <v>0.3575</v>
+      </c>
+      <c r="BU118" t="n">
+        <v>0.28119</v>
+      </c>
+      <c r="BV118" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BW118" t="n">
+        <v>0.2583</v>
+      </c>
+      <c r="BX118" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BY118" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BZ118" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CA118" t="n">
+        <v>0.68289</v>
+      </c>
+      <c r="CB118" t="n">
+        <v>0.78498</v>
+      </c>
+      <c r="CC118" t="n">
+        <v>0.77036</v>
+      </c>
+      <c r="CD118" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CE118" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CF118" t="n">
+        <v>0.79062</v>
+      </c>
+      <c r="CG118" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CH118" t="n">
+        <v>0.30698</v>
+      </c>
+      <c r="CI118" t="n">
+        <v>0.47635</v>
+      </c>
+      <c r="CJ118" t="n">
+        <v>0.13508</v>
+      </c>
+      <c r="CK118" t="n">
+        <v>0.44195</v>
+      </c>
+      <c r="CL118" t="n">
+        <v>0.60233</v>
+      </c>
+      <c r="CM118" t="n">
+        <v>0.44029</v>
+      </c>
+      <c r="CN118" t="n">
+        <v>0.43437</v>
+      </c>
+      <c r="CO118" t="n">
+        <v>0.4035</v>
+      </c>
+      <c r="CP118" t="n">
+        <v>0.33775</v>
+      </c>
+      <c r="CQ118" t="n">
+        <v>0.37665</v>
+      </c>
+      <c r="CR118" t="n">
+        <v>0.35358</v>
+      </c>
+      <c r="CS118" t="n">
+        <v>0.33314</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="2" t="n">
+        <v>46140</v>
+      </c>
+      <c r="B119" t="n">
+        <v>0.32157</v>
+      </c>
+      <c r="C119" t="n">
+        <v>0.5164099999999999</v>
+      </c>
+      <c r="D119" t="n">
+        <v>0.37171</v>
+      </c>
+      <c r="E119" t="n">
+        <v>0.48592</v>
+      </c>
+      <c r="F119" t="n">
+        <v>0.37981</v>
+      </c>
+      <c r="G119" t="n">
+        <v>0.38126</v>
+      </c>
+      <c r="H119" t="n">
+        <v>0.40251</v>
+      </c>
+      <c r="I119" t="n">
+        <v>0.39365</v>
+      </c>
+      <c r="J119" t="n">
+        <v>0.39101</v>
+      </c>
+      <c r="K119" t="n">
+        <v>0.38255</v>
+      </c>
+      <c r="L119" t="n">
+        <v>0.36187</v>
+      </c>
+      <c r="M119" t="n">
+        <v>0.4343</v>
+      </c>
+      <c r="N119" t="n">
+        <v>0.45073</v>
+      </c>
+      <c r="O119" t="n">
+        <v>0.33604</v>
+      </c>
+      <c r="P119" t="n">
+        <v>0.37171</v>
+      </c>
+      <c r="Q119" t="n">
+        <v>0.39328</v>
+      </c>
+      <c r="R119" t="n">
+        <v>0.36484</v>
+      </c>
+      <c r="S119" t="n">
+        <v>0.37068</v>
+      </c>
+      <c r="T119" t="n">
+        <v>0.35233</v>
+      </c>
+      <c r="U119" t="n">
+        <v>0.35765</v>
+      </c>
+      <c r="V119" t="n">
+        <v>0.34746</v>
+      </c>
+      <c r="W119" t="n">
+        <v>0.36179</v>
+      </c>
+      <c r="X119" t="n">
+        <v>0.35519</v>
+      </c>
+      <c r="Y119" t="n">
+        <v>0.37864</v>
+      </c>
+      <c r="Z119" t="n">
+        <v>0.39645</v>
+      </c>
+      <c r="AA119" t="n">
+        <v>0.47425</v>
+      </c>
+      <c r="AB119" t="n">
+        <v>0.45011</v>
+      </c>
+      <c r="AC119" t="n">
+        <v>0.44456</v>
+      </c>
+      <c r="AD119" t="n">
+        <v>0.34906</v>
+      </c>
+      <c r="AE119" t="n">
+        <v>0.39714</v>
+      </c>
+      <c r="AF119" t="n">
+        <v>0.35285</v>
+      </c>
+      <c r="AG119" t="n">
+        <v>0.36885</v>
+      </c>
+      <c r="AH119" t="n">
+        <v>0.34683</v>
+      </c>
+      <c r="AI119" t="n">
+        <v>0.21084</v>
+      </c>
+      <c r="AJ119" t="n">
+        <v>0.28977</v>
+      </c>
+      <c r="AK119" t="n">
+        <v>0.29551</v>
+      </c>
+      <c r="AL119" t="n">
+        <v>0.30859</v>
+      </c>
+      <c r="AM119" t="n">
+        <v>-0.015</v>
+      </c>
+      <c r="AN119" t="n">
+        <v>0.26303</v>
+      </c>
+      <c r="AO119" t="n">
+        <v>0.24914</v>
+      </c>
+      <c r="AP119" t="n">
+        <v>0.30559</v>
+      </c>
+      <c r="AQ119" t="n">
+        <v>0.30868</v>
+      </c>
+      <c r="AR119" t="n">
+        <v>0.29679</v>
+      </c>
+      <c r="AS119" t="n">
+        <v>0.28252</v>
+      </c>
+      <c r="AT119" t="n">
+        <v>0.3364</v>
+      </c>
+      <c r="AU119" t="n">
+        <v>0.27279</v>
+      </c>
+      <c r="AV119" t="n">
+        <v>0.25765</v>
+      </c>
+      <c r="AW119" t="n">
+        <v>0.13541</v>
+      </c>
+      <c r="AX119" t="n">
+        <v>0.09068999999999999</v>
+      </c>
+      <c r="AY119" t="n">
+        <v>0.22901</v>
+      </c>
+      <c r="AZ119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BA119" t="n">
+        <v>0.27676</v>
+      </c>
+      <c r="BB119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BC119" t="n">
+        <v>0.01628</v>
+      </c>
+      <c r="BD119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BE119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BF119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BG119" t="n">
+        <v>0.16869</v>
+      </c>
+      <c r="BH119" t="n">
+        <v>0.29137</v>
+      </c>
+      <c r="BI119" t="n">
+        <v>0.33564</v>
+      </c>
+      <c r="BJ119" t="n">
+        <v>0.29822</v>
+      </c>
+      <c r="BK119" t="n">
+        <v>0.27819</v>
+      </c>
+      <c r="BL119" t="n">
+        <v>0.201</v>
+      </c>
+      <c r="BM119" t="n">
+        <v>0.15487</v>
+      </c>
+      <c r="BN119" t="n">
+        <v>0.00143</v>
+      </c>
+      <c r="BO119" t="n">
+        <v>0.08416999999999999</v>
+      </c>
+      <c r="BP119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BQ119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BR119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BS119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BT119" t="n">
+        <v>0.0539</v>
+      </c>
+      <c r="BU119" t="n">
+        <v>0.1975</v>
+      </c>
+      <c r="BV119" t="n">
+        <v>0.27103</v>
+      </c>
+      <c r="BW119" t="n">
+        <v>0.31541</v>
+      </c>
+      <c r="BX119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BY119" t="n">
+        <v>0.18471</v>
+      </c>
+      <c r="BZ119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CA119" t="n">
+        <v>0.26087</v>
+      </c>
+      <c r="CB119" t="n">
+        <v>0.28216</v>
+      </c>
+      <c r="CC119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CD119" t="n">
+        <v>-0.008019999999999999</v>
+      </c>
+      <c r="CE119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CF119" t="n">
+        <v>0.07540999999999999</v>
+      </c>
+      <c r="CG119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CH119" t="n">
+        <v>0.20486</v>
+      </c>
+      <c r="CI119" t="n">
+        <v>0.2257</v>
+      </c>
+      <c r="CJ119" t="n">
+        <v>0.21178</v>
+      </c>
+      <c r="CK119" t="n">
+        <v>0.05343999999999999</v>
+      </c>
+      <c r="CL119" t="n">
+        <v>0.14055</v>
+      </c>
+      <c r="CM119" t="n">
+        <v>0.08904999999999999</v>
+      </c>
+      <c r="CN119" t="n">
+        <v>0.09905</v>
+      </c>
+      <c r="CO119" t="n">
+        <v>0.24019</v>
+      </c>
+      <c r="CP119" t="n">
+        <v>0.22269</v>
+      </c>
+      <c r="CQ119" t="n">
+        <v>0.2759</v>
+      </c>
+      <c r="CR119" t="n">
+        <v>0.34954</v>
+      </c>
+      <c r="CS119" t="n">
+        <v>0.3432</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="2" t="n">
+        <v>46141</v>
+      </c>
+      <c r="B120" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="C120" t="n">
+        <v>0.09529</v>
+      </c>
+      <c r="D120" t="n">
+        <v>0.24816</v>
+      </c>
+      <c r="E120" t="n">
+        <v>0.32276</v>
+      </c>
+      <c r="F120" t="n">
+        <v>0.28764</v>
+      </c>
+      <c r="G120" t="n">
+        <v>0.24842</v>
+      </c>
+      <c r="H120" t="n">
+        <v>0.3459100000000001</v>
+      </c>
+      <c r="I120" t="n">
+        <v>0.33469</v>
+      </c>
+      <c r="J120" t="n">
+        <v>0.32846</v>
+      </c>
+      <c r="K120" t="n">
+        <v>0.33368</v>
+      </c>
+      <c r="L120" t="n">
+        <v>0.30425</v>
+      </c>
+      <c r="M120" t="n">
+        <v>0.30478</v>
+      </c>
+      <c r="N120" t="n">
+        <v>0.46901</v>
+      </c>
+      <c r="O120" t="n">
+        <v>0.31525</v>
+      </c>
+      <c r="P120" t="n">
+        <v>0.31934</v>
+      </c>
+      <c r="Q120" t="n">
+        <v>0.30477</v>
+      </c>
+      <c r="R120" t="n">
+        <v>0.31913</v>
+      </c>
+      <c r="S120" t="n">
+        <v>0.3193</v>
+      </c>
+      <c r="T120" t="n">
+        <v>0.29742</v>
+      </c>
+      <c r="U120" t="n">
+        <v>0.30001</v>
+      </c>
+      <c r="V120" t="n">
+        <v>0.29652</v>
+      </c>
+      <c r="W120" t="n">
+        <v>0.29428</v>
+      </c>
+      <c r="X120" t="n">
+        <v>0.29698</v>
+      </c>
+      <c r="Y120" t="n">
+        <v>0.33719</v>
+      </c>
+      <c r="Z120" t="n">
+        <v>0.33924</v>
+      </c>
+      <c r="AA120" t="n">
+        <v>0.3594</v>
+      </c>
+      <c r="AB120" t="n">
+        <v>0.3439</v>
+      </c>
+      <c r="AC120" t="n">
+        <v>0.39057</v>
+      </c>
+      <c r="AD120" t="n">
+        <v>0.32169</v>
+      </c>
+      <c r="AE120" t="n">
+        <v>0.32982</v>
+      </c>
+      <c r="AF120" t="n">
+        <v>0.31163</v>
+      </c>
+      <c r="AG120" t="n">
+        <v>0.29932</v>
+      </c>
+      <c r="AH120" t="n">
+        <v>0.3412</v>
+      </c>
+      <c r="AI120" t="n">
+        <v>0.24771</v>
+      </c>
+      <c r="AJ120" t="n">
+        <v>0.28259</v>
+      </c>
+      <c r="AK120" t="n">
+        <v>0.26564</v>
+      </c>
+      <c r="AL120" t="n">
+        <v>0.05283</v>
+      </c>
+      <c r="AM120" t="n">
+        <v>0.00519</v>
+      </c>
+      <c r="AN120" t="n">
+        <v>-0.03653</v>
+      </c>
+      <c r="AO120" t="n">
+        <v>-0.009480000000000001</v>
+      </c>
+      <c r="AP120" t="n">
+        <v>0.27456</v>
+      </c>
+      <c r="AQ120" t="n">
+        <v>0.23493</v>
+      </c>
+      <c r="AR120" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AS120" t="n">
+        <v>0.28032</v>
+      </c>
+      <c r="AT120" t="n">
+        <v>0.27767</v>
+      </c>
+      <c r="AU120" t="n">
+        <v>0.30326</v>
+      </c>
+      <c r="AV120" t="n">
+        <v>0.38178</v>
+      </c>
+      <c r="AW120" t="n">
+        <v>-0.0484</v>
+      </c>
+      <c r="AX120" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY120" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AZ120" t="n">
+        <v>0.07870000000000001</v>
+      </c>
+      <c r="BA120" t="n">
+        <v>0.16694</v>
+      </c>
+      <c r="BB120" t="n">
+        <v>0.12444</v>
+      </c>
+      <c r="BC120" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BD120" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BE120" t="n">
+        <v>0.00452</v>
+      </c>
+      <c r="BF120" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BG120" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BH120" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BI120" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BJ120" t="n">
+        <v>0.35833</v>
+      </c>
+      <c r="BK120" t="n">
+        <v>0.32227</v>
+      </c>
+      <c r="BL120" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BM120" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BN120" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BO120" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BP120" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BQ120" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BR120" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BS120" t="n">
+        <v>0.0401</v>
+      </c>
+      <c r="BT120" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BU120" t="n">
+        <v>0.02494</v>
+      </c>
+      <c r="BV120" t="n">
+        <v>0.27817</v>
+      </c>
+      <c r="BW120" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BX120" t="n">
+        <v>0.02852</v>
+      </c>
+      <c r="BY120" t="n">
+        <v>0.0905</v>
+      </c>
+      <c r="BZ120" t="n">
+        <v>-0.02324</v>
+      </c>
+      <c r="CA120" t="n">
+        <v>0.02347</v>
+      </c>
+      <c r="CB120" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CC120" t="n">
+        <v>0.16342</v>
+      </c>
+      <c r="CD120" t="n">
+        <v>0.28062</v>
+      </c>
+      <c r="CE120" t="n">
+        <v>0.28199</v>
+      </c>
+      <c r="CF120" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CG120" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CH120" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CI120" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CJ120" t="n">
+        <v>0.27929</v>
+      </c>
+      <c r="CK120" t="n">
+        <v>0.0317</v>
+      </c>
+      <c r="CL120" t="n">
+        <v>0.16988</v>
+      </c>
+      <c r="CM120" t="n">
+        <v>0.30619</v>
+      </c>
+      <c r="CN120" t="n">
+        <v>-0.00617</v>
+      </c>
+      <c r="CO120" t="n">
+        <v>0.29499</v>
+      </c>
+      <c r="CP120" t="n">
+        <v>0.30322</v>
+      </c>
+      <c r="CQ120" t="n">
+        <v>0.31036</v>
+      </c>
+      <c r="CR120" t="n">
+        <v>0.29655</v>
+      </c>
+      <c r="CS120" t="n">
+        <v>0.29586</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="2" t="n">
+        <v>46142</v>
+      </c>
+      <c r="B121" t="n">
+        <v>0.3051</v>
+      </c>
+      <c r="C121" t="n">
+        <v>0.29376</v>
+      </c>
+      <c r="D121" t="n">
+        <v>0.28437</v>
+      </c>
+      <c r="E121" t="n">
+        <v>0.36656</v>
+      </c>
+      <c r="F121" t="n">
+        <v>0.35666</v>
+      </c>
+      <c r="G121" t="n">
+        <v>0.33945</v>
+      </c>
+      <c r="H121" t="n">
+        <v>0.3005</v>
+      </c>
+      <c r="I121" t="n">
+        <v>0.31093</v>
+      </c>
+      <c r="J121" t="n">
+        <v>0.31032</v>
+      </c>
+      <c r="K121" t="n">
+        <v>0.30653</v>
+      </c>
+      <c r="L121" t="n">
+        <v>0.30412</v>
+      </c>
+      <c r="M121" t="n">
+        <v>0.28706</v>
+      </c>
+      <c r="N121" t="n">
+        <v>0.30559</v>
+      </c>
+      <c r="O121" t="n">
+        <v>0.30457</v>
+      </c>
+      <c r="P121" t="n">
+        <v>0.28668</v>
+      </c>
+      <c r="Q121" t="n">
+        <v>0.29064</v>
+      </c>
+      <c r="R121" t="n">
+        <v>0.28967</v>
+      </c>
+      <c r="S121" t="n">
+        <v>0.2896</v>
+      </c>
+      <c r="T121" t="n">
+        <v>0.28949</v>
+      </c>
+      <c r="U121" t="n">
+        <v>0.29775</v>
+      </c>
+      <c r="V121" t="n">
+        <v>0.29172</v>
+      </c>
+      <c r="W121" t="n">
+        <v>0.2948</v>
+      </c>
+      <c r="X121" t="n">
+        <v>0.3124</v>
+      </c>
+      <c r="Y121" t="n">
+        <v>0.30495</v>
+      </c>
+      <c r="Z121" t="n">
+        <v>0.31655</v>
+      </c>
+      <c r="AA121" t="n">
+        <v>0.32447</v>
+      </c>
+      <c r="AB121" t="n">
+        <v>0.32436</v>
+      </c>
+      <c r="AC121" t="n">
+        <v>0.33283</v>
+      </c>
+      <c r="AD121" t="n">
+        <v>0.32616</v>
+      </c>
+      <c r="AE121" t="n">
+        <v>0.27826</v>
+      </c>
+      <c r="AF121" t="n">
+        <v>0.25895</v>
+      </c>
+      <c r="AG121" t="n">
+        <v>0.02527</v>
+      </c>
+      <c r="AH121" t="n">
+        <v>0.03688</v>
+      </c>
+      <c r="AI121" t="n">
+        <v>0.04065999999999999</v>
+      </c>
+      <c r="AJ121" t="n">
+        <v>0.04443</v>
+      </c>
+      <c r="AK121" t="n">
+        <v>0.03959</v>
+      </c>
+      <c r="AL121" t="n">
+        <v>0.03962</v>
+      </c>
+      <c r="AM121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AN121" t="n">
+        <v>-0.01866</v>
+      </c>
+      <c r="AO121" t="n">
+        <v>-0.04424</v>
+      </c>
+      <c r="AP121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AQ121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AR121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AS121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AT121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AU121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AV121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AW121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AX121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AZ121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BA121" t="n">
+        <v>-0.0498</v>
+      </c>
+      <c r="BB121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BC121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BD121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BE121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BF121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BG121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BH121" t="n">
+        <v>-0.04777</v>
+      </c>
+      <c r="BI121" t="n">
+        <v>-0.04921</v>
+      </c>
+      <c r="BJ121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BK121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BL121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BM121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BN121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BO121" t="n">
+        <v>0.14862</v>
+      </c>
+      <c r="BP121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BQ121" t="n">
+        <v>1e-05</v>
+      </c>
+      <c r="BR121" t="n">
+        <v>0.28742</v>
+      </c>
+      <c r="BS121" t="n">
+        <v>0.05241</v>
+      </c>
+      <c r="BT121" t="n">
+        <v>0.14774</v>
+      </c>
+      <c r="BU121" t="n">
+        <v>0.18658</v>
+      </c>
+      <c r="BV121" t="n">
+        <v>0.27237</v>
+      </c>
+      <c r="BW121" t="n">
+        <v>0.17721</v>
+      </c>
+      <c r="BX121" t="n">
+        <v>0.21081</v>
+      </c>
+      <c r="BY121" t="n">
+        <v>0.11685</v>
+      </c>
+      <c r="BZ121" t="n">
+        <v>0.27685</v>
+      </c>
+      <c r="CA121" t="n">
+        <v>0.2183</v>
+      </c>
+      <c r="CB121" t="n">
+        <v>0.28382</v>
+      </c>
+      <c r="CC121" t="n">
+        <v>0.37947</v>
+      </c>
+      <c r="CD121" t="n">
+        <v>0.30275</v>
+      </c>
+      <c r="CE121" t="n">
+        <v>0.30549</v>
+      </c>
+      <c r="CF121" t="n">
+        <v>0.30407</v>
+      </c>
+      <c r="CG121" t="n">
+        <v>0.39949</v>
+      </c>
+      <c r="CH121" t="n">
+        <v>0.39849</v>
+      </c>
+      <c r="CI121" t="n">
+        <v>0.40979</v>
+      </c>
+      <c r="CJ121" t="n">
+        <v>0.4675299999999999</v>
+      </c>
+      <c r="CK121" t="n">
+        <v>0.35384</v>
+      </c>
+      <c r="CL121" t="n">
+        <v>0.39643</v>
+      </c>
+      <c r="CM121" t="n">
+        <v>0.40001</v>
+      </c>
+      <c r="CN121" t="n">
+        <v>0.41352</v>
+      </c>
+      <c r="CO121" t="n">
+        <v>0.355</v>
+      </c>
+      <c r="CP121" t="n">
+        <v>0.35809</v>
+      </c>
+      <c r="CQ121" t="n">
+        <v>0.34467</v>
+      </c>
+      <c r="CR121" t="n">
+        <v>0.3553</v>
+      </c>
+      <c r="CS121" t="n">
+        <v>0.34897</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="2" t="n">
+        <v>46143</v>
+      </c>
+      <c r="B122" t="n">
+        <v>0.368</v>
+      </c>
+      <c r="C122" t="n">
+        <v>0.25046</v>
+      </c>
+      <c r="D122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="E122" t="n">
+        <v>-0.01112</v>
+      </c>
+      <c r="F122" t="n">
+        <v>0.28671</v>
+      </c>
+      <c r="G122" t="n">
+        <v>0.3086</v>
+      </c>
+      <c r="H122" t="n">
+        <v>0.33073</v>
+      </c>
+      <c r="I122" t="n">
+        <v>0.31542</v>
+      </c>
+      <c r="J122" t="n">
+        <v>0.32992</v>
+      </c>
+      <c r="K122" t="n">
+        <v>0.3097200000000001</v>
+      </c>
+      <c r="L122" t="n">
+        <v>0.28182</v>
+      </c>
+      <c r="M122" t="n">
+        <v>0.31068</v>
+      </c>
+      <c r="N122" t="n">
+        <v>0.32946</v>
+      </c>
+      <c r="O122" t="n">
+        <v>0.34482</v>
+      </c>
+      <c r="P122" t="n">
+        <v>0.33233</v>
+      </c>
+      <c r="Q122" t="n">
+        <v>0.331</v>
+      </c>
+      <c r="R122" t="n">
+        <v>0.33092</v>
+      </c>
+      <c r="S122" t="n">
+        <v>0.31463</v>
+      </c>
+      <c r="T122" t="n">
+        <v>0.32233</v>
+      </c>
+      <c r="U122" t="n">
+        <v>0.3365</v>
+      </c>
+      <c r="V122" t="n">
+        <v>0.31042</v>
+      </c>
+      <c r="W122" t="n">
+        <v>0.29954</v>
+      </c>
+      <c r="X122" t="n">
+        <v>0.31043</v>
+      </c>
+      <c r="Y122" t="n">
+        <v>0.33531</v>
+      </c>
+      <c r="Z122" t="n">
+        <v>0.33879</v>
+      </c>
+      <c r="AA122" t="n">
+        <v>0.35002</v>
+      </c>
+      <c r="AB122" t="n">
+        <v>0.35201</v>
+      </c>
+      <c r="AC122" t="n">
+        <v>0.34243</v>
+      </c>
+      <c r="AD122" t="n">
+        <v>0.31601</v>
+      </c>
+      <c r="AE122" t="n">
+        <v>0.10251</v>
+      </c>
+      <c r="AF122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AG122" t="n">
+        <v>-0.04958</v>
+      </c>
+      <c r="AH122" t="n">
+        <v>-0.0466</v>
+      </c>
+      <c r="AI122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AJ122" t="n">
+        <v>-0.04572</v>
+      </c>
+      <c r="AK122" t="n">
+        <v>-0.04577000000000001</v>
+      </c>
+      <c r="AL122" t="n">
+        <v>-0.04572</v>
+      </c>
+      <c r="AM122" t="n">
+        <v>-0.04505</v>
+      </c>
+      <c r="AN122" t="n">
+        <v>-0.04321</v>
+      </c>
+      <c r="AO122" t="n">
+        <v>-0.04218</v>
+      </c>
+      <c r="AP122" t="n">
+        <v>-0.04456</v>
+      </c>
+      <c r="AQ122" t="n">
+        <v>0.1012</v>
+      </c>
+      <c r="AR122" t="n">
+        <v>-0.00259</v>
+      </c>
+      <c r="AS122" t="n">
+        <v>-0.04365</v>
+      </c>
+      <c r="AT122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AU122" t="n">
+        <v>-0.04566</v>
+      </c>
+      <c r="AV122" t="n">
+        <v>-0.04297</v>
+      </c>
+      <c r="AW122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AX122" t="n">
+        <v>-0.04856</v>
+      </c>
+      <c r="AY122" t="n">
+        <v>-0.04845</v>
+      </c>
+      <c r="AZ122" t="n">
+        <v>-0.04488</v>
+      </c>
+      <c r="BA122" t="n">
+        <v>-0.04341</v>
+      </c>
+      <c r="BB122" t="n">
+        <v>-0.04233</v>
+      </c>
+      <c r="BC122" t="n">
+        <v>-0.04823</v>
+      </c>
+      <c r="BD122" t="n">
+        <v>-0.0485</v>
+      </c>
+      <c r="BE122" t="n">
+        <v>-0.04243</v>
+      </c>
+      <c r="BF122" t="n">
+        <v>-0.04983</v>
+      </c>
+      <c r="BG122" t="n">
+        <v>-0.04813</v>
+      </c>
+      <c r="BH122" t="n">
+        <v>-0.04478</v>
+      </c>
+      <c r="BI122" t="n">
+        <v>-0.04888</v>
+      </c>
+      <c r="BJ122" t="n">
+        <v>-0.04349</v>
+      </c>
+      <c r="BK122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BL122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BM122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BN122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BO122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BP122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BQ122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BR122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BS122" t="n">
+        <v>0.07164</v>
+      </c>
+      <c r="BT122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BU122" t="n">
+        <v>0.17789</v>
+      </c>
+      <c r="BV122" t="n">
+        <v>0.2368</v>
+      </c>
+      <c r="BW122" t="n">
+        <v>0.2546</v>
+      </c>
+      <c r="BX122" t="n">
+        <v>0.25494</v>
+      </c>
+      <c r="BY122" t="n">
+        <v>0.24718</v>
+      </c>
+      <c r="BZ122" t="n">
+        <v>0.2879</v>
+      </c>
+      <c r="CA122" t="n">
+        <v>0.14479</v>
+      </c>
+      <c r="CB122" t="n">
+        <v>0.21643</v>
+      </c>
+      <c r="CC122" t="n">
+        <v>0.19304</v>
+      </c>
+      <c r="CD122" t="n">
+        <v>0.21196</v>
+      </c>
+      <c r="CE122" t="n">
+        <v>0.22219</v>
+      </c>
+      <c r="CF122" t="n">
+        <v>0.19587</v>
+      </c>
+      <c r="CG122" t="n">
+        <v>0.21719</v>
+      </c>
+      <c r="CH122" t="n">
+        <v>0.19675</v>
+      </c>
+      <c r="CI122" t="n">
+        <v>0.24315</v>
+      </c>
+      <c r="CJ122" t="n">
+        <v>0.23636</v>
+      </c>
+      <c r="CK122" t="n">
+        <v>0.25857</v>
+      </c>
+      <c r="CL122" t="n">
+        <v>0.29535</v>
+      </c>
+      <c r="CM122" t="n">
+        <v>0.28178</v>
+      </c>
+      <c r="CN122" t="n">
+        <v>0.31044</v>
+      </c>
+      <c r="CO122" t="n">
+        <v>0.33942</v>
+      </c>
+      <c r="CP122" t="n">
+        <v>0.34548</v>
+      </c>
+      <c r="CQ122" t="n">
+        <v>0.36746</v>
+      </c>
+      <c r="CR122" t="n">
+        <v>0.36595</v>
+      </c>
+      <c r="CS122" t="n">
+        <v>0.33053</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="2" t="n">
+        <v>46144</v>
+      </c>
+      <c r="B123" t="n">
+        <v>0.33124</v>
+      </c>
+      <c r="C123" t="n">
+        <v>1.31872</v>
+      </c>
+      <c r="D123" t="n">
+        <v>0.30565</v>
+      </c>
+      <c r="E123" t="n">
+        <v>0.40549</v>
+      </c>
+      <c r="F123" t="n">
+        <v>0.33102</v>
+      </c>
+      <c r="G123" t="n">
+        <v>0.32158</v>
+      </c>
+      <c r="H123" t="n">
+        <v>0.30194</v>
+      </c>
+      <c r="I123" t="n">
+        <v>0.31134</v>
+      </c>
+      <c r="J123" t="n">
+        <v>0.27864</v>
+      </c>
+      <c r="K123" t="n">
+        <v>0.25854</v>
+      </c>
+      <c r="L123" t="n">
+        <v>0.10287</v>
+      </c>
+      <c r="M123" t="n">
+        <v>0.29157</v>
+      </c>
+      <c r="N123" t="n">
+        <v>0.24693</v>
+      </c>
+      <c r="O123" t="n">
+        <v>0.25979</v>
+      </c>
+      <c r="P123" t="n">
+        <v>0.2458</v>
+      </c>
+      <c r="Q123" t="n">
+        <v>0.27147</v>
+      </c>
+      <c r="R123" t="n">
+        <v>0.28154</v>
+      </c>
+      <c r="S123" t="n">
+        <v>0.08112999999999999</v>
+      </c>
+      <c r="T123" t="n">
+        <v>0.05961</v>
+      </c>
+      <c r="U123" t="n">
+        <v>0.17177</v>
+      </c>
+      <c r="V123" t="n">
+        <v>0.14839</v>
+      </c>
+      <c r="W123" t="n">
+        <v>0.16012</v>
+      </c>
+      <c r="X123" t="n">
+        <v>0.15935</v>
+      </c>
+      <c r="Y123" t="n">
+        <v>0.23739</v>
+      </c>
+      <c r="Z123" t="n">
+        <v>0.21477</v>
+      </c>
+      <c r="AA123" t="n">
+        <v>0.17562</v>
+      </c>
+      <c r="AB123" t="n">
+        <v>0.12011</v>
+      </c>
+      <c r="AC123" t="n">
+        <v>0.28644</v>
+      </c>
+      <c r="AD123" t="n">
+        <v>0.27634</v>
+      </c>
+      <c r="AE123" t="n">
+        <v>0.32026</v>
+      </c>
+      <c r="AF123" t="n">
+        <v>0.29142</v>
+      </c>
+      <c r="AG123" t="n">
+        <v>0.25843</v>
+      </c>
+      <c r="AH123" t="n">
+        <v>0.25568</v>
+      </c>
+      <c r="AI123" t="n">
+        <v>0.25506</v>
+      </c>
+      <c r="AJ123" t="n">
+        <v>-0.04602000000000001</v>
+      </c>
+      <c r="AK123" t="n">
+        <v>0.28119</v>
+      </c>
+      <c r="AL123" t="n">
+        <v>0.32352</v>
+      </c>
+      <c r="AM123" t="n">
+        <v>0.29734</v>
+      </c>
+      <c r="AN123" t="n">
+        <v>0.28086</v>
+      </c>
+      <c r="AO123" t="n">
+        <v>0.2568</v>
+      </c>
+      <c r="AP123" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AQ123" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AR123" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AS123" t="n">
+        <v>-0.01281</v>
+      </c>
+      <c r="AT123" t="n">
+        <v>0.12149</v>
+      </c>
+      <c r="AU123" t="n">
+        <v>0.07418000000000001</v>
+      </c>
+      <c r="AV123" t="n">
+        <v>-0.00099</v>
+      </c>
+      <c r="AW123" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AX123" t="n">
+        <v>0.3058</v>
+      </c>
+      <c r="AY123" t="n">
+        <v>0.36106</v>
+      </c>
+      <c r="AZ123" t="n">
+        <v>0.15108</v>
+      </c>
+      <c r="BA123" t="n">
+        <v>0.10934</v>
+      </c>
+      <c r="BB123" t="n">
+        <v>-0.00021</v>
+      </c>
+      <c r="BC123" t="n">
+        <v>0.05401</v>
+      </c>
+      <c r="BD123" t="n">
+        <v>0.10872</v>
+      </c>
+      <c r="BE123" t="n">
+        <v>0.2965</v>
+      </c>
+      <c r="BF123" t="n">
+        <v>0.17805</v>
+      </c>
+      <c r="BG123" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BH123" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BI123" t="n">
+        <v>0.27373</v>
+      </c>
+      <c r="BJ123" t="n">
+        <v>0.31171</v>
+      </c>
+      <c r="BK123" t="n">
+        <v>-0.04998</v>
+      </c>
+      <c r="BL123" t="n">
+        <v>0.32106</v>
+      </c>
+      <c r="BM123" t="n">
+        <v>0.16755</v>
+      </c>
+      <c r="BN123" t="n">
+        <v>-0.0496</v>
+      </c>
+      <c r="BO123" t="n">
+        <v>0.07872</v>
+      </c>
+      <c r="BP123" t="n">
+        <v>0.20561</v>
+      </c>
+      <c r="BQ123" t="n">
+        <v>0.47798</v>
+      </c>
+      <c r="BR123" t="n">
+        <v>0.32667</v>
+      </c>
+      <c r="BS123" t="n">
+        <v>0.73982</v>
+      </c>
+      <c r="BT123" t="n">
+        <v>0.49035</v>
+      </c>
+      <c r="BU123" t="n">
+        <v>0.78532</v>
+      </c>
+      <c r="BV123" t="n">
+        <v>0.23584</v>
+      </c>
+      <c r="BW123" t="n">
+        <v>0.29821</v>
+      </c>
+      <c r="BX123" t="n">
+        <v>0.5764</v>
+      </c>
+      <c r="BY123" t="n">
+        <v>0.52227</v>
+      </c>
+      <c r="BZ123" t="n">
+        <v>0.2089</v>
+      </c>
+      <c r="CA123" t="n">
+        <v>0.4909</v>
+      </c>
+      <c r="CB123" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CC123" t="n">
+        <v>0.9364600000000001</v>
+      </c>
+      <c r="CD123" t="n">
+        <v>-0.01115</v>
+      </c>
+      <c r="CE123" t="n">
+        <v>0.4913</v>
+      </c>
+      <c r="CF123" t="n">
+        <v>0.323</v>
+      </c>
+      <c r="CG123" t="n">
+        <v>0.6919500000000001</v>
+      </c>
+      <c r="CH123" t="n">
+        <v>0.47638</v>
+      </c>
+      <c r="CI123" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CJ123" t="n">
+        <v>0.9828</v>
+      </c>
+      <c r="CK123" t="n">
+        <v>0.70156</v>
+      </c>
+      <c r="CL123" t="n">
+        <v>0.33919</v>
+      </c>
+      <c r="CM123" t="n">
+        <v>0.7900700000000001</v>
+      </c>
+      <c r="CN123" t="n">
+        <v>0.5303300000000001</v>
+      </c>
+      <c r="CO123" t="n">
+        <v>0.7873300000000001</v>
+      </c>
+      <c r="CP123" t="n">
+        <v>0.7767999999999999</v>
+      </c>
+      <c r="CQ123" t="n">
+        <v>0.87854</v>
+      </c>
+      <c r="CR123" t="n">
+        <v>0.87338</v>
+      </c>
+      <c r="CS123" t="n">
+        <v>0.49228</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="2" t="n">
+        <v>46145</v>
+      </c>
+      <c r="B124" t="n">
+        <v>0.41176</v>
+      </c>
+      <c r="C124" t="n">
+        <v>1.39917</v>
+      </c>
+      <c r="D124" t="n">
+        <v>0.44916</v>
+      </c>
+      <c r="E124" t="n">
+        <v>1.20629</v>
+      </c>
+      <c r="F124" t="n">
+        <v>0.87936</v>
+      </c>
+      <c r="G124" t="n">
+        <v>0.5513400000000001</v>
+      </c>
+      <c r="H124" t="n">
+        <v>0.6389400000000001</v>
+      </c>
+      <c r="I124" t="n">
+        <v>0.53832</v>
+      </c>
+      <c r="J124" t="n">
+        <v>0.49859</v>
+      </c>
+      <c r="K124" t="n">
+        <v>0.45896</v>
+      </c>
+      <c r="L124" t="n">
+        <v>0.42742</v>
+      </c>
+      <c r="M124" t="n">
+        <v>0.44127</v>
+      </c>
+      <c r="N124" t="n">
+        <v>0.45119</v>
+      </c>
+      <c r="O124" t="n">
+        <v>0.39345</v>
+      </c>
+      <c r="P124" t="n">
+        <v>0.45398</v>
+      </c>
+      <c r="Q124" t="n">
+        <v>0.42111</v>
+      </c>
+      <c r="R124" t="n">
+        <v>0.35485</v>
+      </c>
+      <c r="S124" t="n">
+        <v>0.40082</v>
+      </c>
+      <c r="T124" t="n">
+        <v>0.3662</v>
+      </c>
+      <c r="U124" t="n">
+        <v>0.37599</v>
+      </c>
+      <c r="V124" t="n">
+        <v>0.41493</v>
+      </c>
+      <c r="W124" t="n">
+        <v>0.43394</v>
+      </c>
+      <c r="X124" t="n">
+        <v>0.34401</v>
+      </c>
+      <c r="Y124" t="n">
+        <v>0.3918</v>
+      </c>
+      <c r="Z124" t="n">
+        <v>0.33179</v>
+      </c>
+      <c r="AA124" t="n">
+        <v>0.35456</v>
+      </c>
+      <c r="AB124" t="n">
+        <v>0.34931</v>
+      </c>
+      <c r="AC124" t="n">
+        <v>0.32873</v>
+      </c>
+      <c r="AD124" t="n">
+        <v>0.39561</v>
+      </c>
+      <c r="AE124" t="n">
+        <v>0.32882</v>
+      </c>
+      <c r="AF124" t="n">
+        <v>0.45181</v>
+      </c>
+      <c r="AG124" t="n">
+        <v>0.35681</v>
+      </c>
+      <c r="AH124" t="n">
+        <v>0.33067</v>
+      </c>
+      <c r="AI124" t="n">
+        <v>0.40084</v>
+      </c>
+      <c r="AJ124" t="n">
+        <v>0.5870700000000001</v>
+      </c>
+      <c r="AK124" t="n">
+        <v>0.42765</v>
+      </c>
+      <c r="AL124" t="n">
+        <v>0.59622</v>
+      </c>
+      <c r="AM124" t="n">
+        <v>0.45198</v>
+      </c>
+      <c r="AN124" t="n">
+        <v>0.65527</v>
+      </c>
+      <c r="AO124" t="n">
+        <v>0.33335</v>
+      </c>
+      <c r="AP124" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AQ124" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AR124" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AS124" t="n">
+        <v>0.8273400000000001</v>
+      </c>
+      <c r="AT124" t="n">
+        <v>-0.00623</v>
+      </c>
+      <c r="AU124" t="n">
+        <v>-0.04745000000000001</v>
+      </c>
+      <c r="AV124" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AW124" t="n">
+        <v>0.83312</v>
+      </c>
+      <c r="AX124" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY124" t="n">
+        <v>0.41649</v>
+      </c>
+      <c r="AZ124" t="n">
+        <v>0.32552</v>
+      </c>
+      <c r="BA124" t="n">
+        <v>-0.04961</v>
+      </c>
+      <c r="BB124" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BC124" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BD124" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BE124" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BF124" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BG124" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BH124" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BI124" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BJ124" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BK124" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BL124" t="n">
+        <v>0.10047</v>
+      </c>
+      <c r="BM124" t="n">
+        <v>0.30996</v>
+      </c>
+      <c r="BN124" t="n">
+        <v>0.0761</v>
+      </c>
+      <c r="BO124" t="n">
+        <v>0.10185</v>
+      </c>
+      <c r="BP124" t="n">
+        <v>0.07314</v>
+      </c>
+      <c r="BQ124" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BR124" t="n">
+        <v>0.09425</v>
+      </c>
+      <c r="BS124" t="n">
+        <v>0.06553</v>
+      </c>
+      <c r="BT124" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BU124" t="n">
+        <v>0.08348</v>
+      </c>
+      <c r="BV124" t="n">
+        <v>0.04538</v>
+      </c>
+      <c r="BW124" t="n">
+        <v>0.06484999999999999</v>
+      </c>
+      <c r="BX124" t="n">
+        <v>0.14029</v>
+      </c>
+      <c r="BY124" t="n">
+        <v>0.07339</v>
+      </c>
+      <c r="BZ124" t="n">
+        <v>0.05197</v>
+      </c>
+      <c r="CA124" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CB124" t="n">
+        <v>0.06648</v>
+      </c>
+      <c r="CC124" t="n">
+        <v>-0.02338</v>
+      </c>
+      <c r="CD124" t="n">
+        <v>0.06902</v>
+      </c>
+      <c r="CE124" t="n">
+        <v>0.07848000000000001</v>
+      </c>
+      <c r="CF124" t="n">
+        <v>0.1296</v>
+      </c>
+      <c r="CG124" t="n">
+        <v>0.12352</v>
+      </c>
+      <c r="CH124" t="n">
+        <v>0.13543</v>
+      </c>
+      <c r="CI124" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CJ124" t="n">
+        <v>0.11894</v>
+      </c>
+      <c r="CK124" t="n">
+        <v>0.22441</v>
+      </c>
+      <c r="CL124" t="n">
+        <v>0.28858</v>
+      </c>
+      <c r="CM124" t="n">
+        <v>0.34442</v>
+      </c>
+      <c r="CN124" t="n">
+        <v>0.41384</v>
+      </c>
+      <c r="CO124" t="n">
+        <v>0.45343</v>
+      </c>
+      <c r="CP124" t="n">
+        <v>0.41618</v>
+      </c>
+      <c r="CQ124" t="n">
+        <v>0.39279</v>
+      </c>
+      <c r="CR124" t="n">
+        <v>0.3763</v>
+      </c>
+      <c r="CS124" t="n">
+        <v>0.3543</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="2" t="n">
+        <v>46146</v>
+      </c>
+      <c r="B125" t="n">
+        <v>0.32925</v>
+      </c>
+      <c r="C125" t="n">
+        <v>0.9549299999999999</v>
+      </c>
+      <c r="D125" t="n">
+        <v>0.36056</v>
+      </c>
+      <c r="E125" t="n">
+        <v>0.46757</v>
+      </c>
+      <c r="F125" t="n">
+        <v>0.4077</v>
+      </c>
+      <c r="G125" t="n">
+        <v>0.4199</v>
+      </c>
+      <c r="H125" t="n">
+        <v>0.47739</v>
+      </c>
+      <c r="I125" t="n">
+        <v>0.38356</v>
+      </c>
+      <c r="J125" t="n">
+        <v>0.41091</v>
+      </c>
+      <c r="K125" t="n">
+        <v>0.36613</v>
+      </c>
+      <c r="L125" t="n">
+        <v>0.33128</v>
+      </c>
+      <c r="M125" t="n">
+        <v>0.35383</v>
+      </c>
+      <c r="N125" t="n">
+        <v>0.34842</v>
+      </c>
+      <c r="O125" t="n">
+        <v>0.28963</v>
+      </c>
+      <c r="P125" t="n">
+        <v>0.33068</v>
+      </c>
+      <c r="Q125" t="n">
+        <v>0.35925</v>
+      </c>
+      <c r="R125" t="n">
+        <v>0.34578</v>
+      </c>
+      <c r="S125" t="n">
+        <v>0.32305</v>
+      </c>
+      <c r="T125" t="n">
+        <v>0.40089</v>
+      </c>
+      <c r="U125" t="n">
+        <v>0.50004</v>
+      </c>
+      <c r="V125" t="n">
+        <v>0.35719</v>
+      </c>
+      <c r="W125" t="n">
+        <v>0.38767</v>
+      </c>
+      <c r="X125" t="n">
+        <v>0.34356</v>
+      </c>
+      <c r="Y125" t="n">
+        <v>0.35091</v>
+      </c>
+      <c r="Z125" t="n">
+        <v>0.35529</v>
+      </c>
+      <c r="AA125" t="n">
+        <v>0.37062</v>
+      </c>
+      <c r="AB125" t="n">
+        <v>0.35772</v>
+      </c>
+      <c r="AC125" t="n">
+        <v>0.36285</v>
+      </c>
+      <c r="AD125" t="n">
+        <v>0.31632</v>
+      </c>
+      <c r="AE125" t="n">
+        <v>0.31347</v>
+      </c>
+      <c r="AF125" t="n">
+        <v>0.33246</v>
+      </c>
+      <c r="AG125" t="n">
+        <v>0.33801</v>
+      </c>
+      <c r="AH125" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AI125" t="n">
+        <v>0.30133</v>
+      </c>
+      <c r="AJ125" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AK125" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AL125" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AM125" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AN125" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AO125" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AP125" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AQ125" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AR125" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AS125" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AT125" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AU125" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AV125" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AW125" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AX125" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY125" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AZ125" t="n">
+        <v>0.06272999999999999</v>
+      </c>
+      <c r="BA125" t="n">
+        <v>0.22856</v>
+      </c>
+      <c r="BB125" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BC125" t="n">
+        <v>0.26014</v>
+      </c>
+      <c r="BD125" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BE125" t="n">
+        <v>0.3005</v>
+      </c>
+      <c r="BF125" t="n">
+        <v>-0.044</v>
+      </c>
+      <c r="BG125" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BH125" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BI125" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BJ125" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BK125" t="n">
+        <v>0.09791</v>
+      </c>
+      <c r="BL125" t="n">
+        <v>0.27256</v>
+      </c>
+      <c r="BM125" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BN125" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BO125" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BP125" t="n">
+        <v>0.2518</v>
+      </c>
+      <c r="BQ125" t="n">
+        <v>0.1033</v>
+      </c>
+      <c r="BR125" t="n">
+        <v>0.2891</v>
+      </c>
+      <c r="BS125" t="n">
+        <v>0.30811</v>
+      </c>
+      <c r="BT125" t="n">
+        <v>0.25429</v>
+      </c>
+      <c r="BU125" t="n">
+        <v>0.35001</v>
+      </c>
+      <c r="BV125" t="n">
+        <v>0.32192</v>
+      </c>
+      <c r="BW125" t="n">
+        <v>0.2722</v>
+      </c>
+      <c r="BX125" t="n">
+        <v>0.2964</v>
+      </c>
+      <c r="BY125" t="n">
+        <v>0.19369</v>
+      </c>
+      <c r="BZ125" t="n">
+        <v>0.29765</v>
+      </c>
+      <c r="CA125" t="n">
+        <v>0.32731</v>
+      </c>
+      <c r="CB125" t="n">
+        <v>0.3197</v>
+      </c>
+      <c r="CC125" t="n">
+        <v>0.30951</v>
+      </c>
+      <c r="CD125" t="n">
+        <v>0.34011</v>
+      </c>
+      <c r="CE125" t="n">
+        <v>0.3179</v>
+      </c>
+      <c r="CF125" t="n">
+        <v>0.38897</v>
+      </c>
+      <c r="CG125" t="n">
+        <v>0.37869</v>
+      </c>
+      <c r="CH125" t="n">
+        <v>0.4325</v>
+      </c>
+      <c r="CI125" t="n">
+        <v>0.349</v>
+      </c>
+      <c r="CJ125" t="n">
+        <v>0.28266</v>
+      </c>
+      <c r="CK125" t="n">
+        <v>0.4232</v>
+      </c>
+      <c r="CL125" t="n">
+        <v>0.34987</v>
+      </c>
+      <c r="CM125" t="n">
+        <v>0.44783</v>
+      </c>
+      <c r="CN125" t="n">
+        <v>0.31938</v>
+      </c>
+      <c r="CO125" t="n">
+        <v>0.42042</v>
+      </c>
+      <c r="CP125" t="n">
+        <v>0.35896</v>
+      </c>
+      <c r="CQ125" t="n">
+        <v>0.4017</v>
+      </c>
+      <c r="CR125" t="n">
+        <v>0.40043</v>
+      </c>
+      <c r="CS125" t="n">
+        <v>0.5967</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="2" t="n">
+        <v>46147</v>
+      </c>
+      <c r="B126" t="n">
+        <v>0.35003</v>
+      </c>
+      <c r="C126" t="n">
+        <v>0.8855499999999999</v>
+      </c>
+      <c r="D126" t="n">
+        <v>1.33379</v>
+      </c>
+      <c r="E126" t="n">
+        <v>1.13584</v>
+      </c>
+      <c r="F126" t="n">
+        <v>0.70345</v>
+      </c>
+      <c r="G126" t="n">
+        <v>0.79516</v>
+      </c>
+      <c r="H126" t="n">
+        <v>0.6496799999999999</v>
+      </c>
+      <c r="I126" t="n">
+        <v>0.58348</v>
+      </c>
+      <c r="J126" t="n">
+        <v>0.45041</v>
+      </c>
+      <c r="K126" t="n">
+        <v>0.45034</v>
+      </c>
+      <c r="L126" t="n">
+        <v>0.50049</v>
+      </c>
+      <c r="M126" t="n">
+        <v>0.4399</v>
+      </c>
+      <c r="N126" t="n">
+        <v>0.43745</v>
+      </c>
+      <c r="O126" t="n">
+        <v>0.41503</v>
+      </c>
+      <c r="P126" t="n">
+        <v>0.41292</v>
+      </c>
+      <c r="Q126" t="n">
+        <v>0.42351</v>
+      </c>
+      <c r="R126" t="n">
+        <v>0.50052</v>
+      </c>
+      <c r="S126" t="n">
+        <v>0.41292</v>
+      </c>
+      <c r="T126" t="n">
+        <v>0.43408</v>
+      </c>
+      <c r="U126" t="n">
+        <v>0.41291</v>
+      </c>
+      <c r="V126" t="n">
+        <v>0.43413</v>
+      </c>
+      <c r="W126" t="n">
+        <v>0.39041</v>
+      </c>
+      <c r="X126" t="n">
+        <v>0.42801</v>
+      </c>
+      <c r="Y126" t="n">
+        <v>0.45039</v>
+      </c>
+      <c r="Z126" t="n">
+        <v>0.3963</v>
+      </c>
+      <c r="AA126" t="n">
+        <v>0.4235</v>
+      </c>
+      <c r="AB126" t="n">
+        <v>0.4341</v>
+      </c>
+      <c r="AC126" t="n">
+        <v>0.41292</v>
+      </c>
+      <c r="AD126" t="n">
+        <v>0.41291</v>
+      </c>
+      <c r="AE126" t="n">
+        <v>0.40025</v>
+      </c>
+      <c r="AF126" t="n">
+        <v>0.42352</v>
+      </c>
+      <c r="AG126" t="n">
+        <v>0.39661</v>
+      </c>
+      <c r="AH126" t="n">
+        <v>0.40248</v>
+      </c>
+      <c r="AI126" t="n">
+        <v>0.3756</v>
+      </c>
+      <c r="AJ126" t="n">
+        <v>0.30923</v>
+      </c>
+      <c r="AK126" t="n">
+        <v>0.01272</v>
+      </c>
+      <c r="AL126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AM126" t="n">
+        <v>-0.04770000000000001</v>
+      </c>
+      <c r="AN126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AO126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AP126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AQ126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AR126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AS126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AT126" t="n">
+        <v>0.23985</v>
+      </c>
+      <c r="AU126" t="n">
+        <v>0.17927</v>
+      </c>
+      <c r="AV126" t="n">
+        <v>-0.04068</v>
+      </c>
+      <c r="AW126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AX126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY126" t="n">
+        <v>0.22579</v>
+      </c>
+      <c r="AZ126" t="n">
+        <v>0.23647</v>
+      </c>
+      <c r="BA126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BB126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BC126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BD126" t="n">
+        <v>0.1951</v>
+      </c>
+      <c r="BE126" t="n">
+        <v>0.04519</v>
+      </c>
+      <c r="BF126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BG126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BH126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BI126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BJ126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BK126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BL126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BM126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BN126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BO126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BP126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BQ126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BR126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BS126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BT126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BU126" t="n">
+        <v>-0.04736</v>
+      </c>
+      <c r="BV126" t="n">
+        <v>-0.00435</v>
+      </c>
+      <c r="BW126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BX126" t="n">
+        <v>-0.04776</v>
+      </c>
+      <c r="BY126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BZ126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CA126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CB126" t="n">
+        <v>-0.005730000000000001</v>
+      </c>
+      <c r="CC126" t="n">
+        <v>-0.04808</v>
+      </c>
+      <c r="CD126" t="n">
+        <v>-0.02603</v>
+      </c>
+      <c r="CE126" t="n">
+        <v>-0.04047</v>
+      </c>
+      <c r="CF126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CG126" t="n">
+        <v>0.1379</v>
+      </c>
+      <c r="CH126" t="n">
+        <v>0.05809</v>
+      </c>
+      <c r="CI126" t="n">
+        <v>0.29148</v>
+      </c>
+      <c r="CJ126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CK126" t="n">
+        <v>0.03393</v>
+      </c>
+      <c r="CL126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CM126" t="n">
+        <v>0.19746</v>
+      </c>
+      <c r="CN126" t="n">
+        <v>0.38578</v>
+      </c>
+      <c r="CO126" t="n">
+        <v>0.36803</v>
+      </c>
+      <c r="CP126" t="n">
+        <v>0.33299</v>
+      </c>
+      <c r="CQ126" t="n">
+        <v>0.34019</v>
+      </c>
+      <c r="CR126" t="n">
+        <v>0.3293</v>
+      </c>
+      <c r="CS126" t="n">
+        <v>0.32475</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="2" t="n">
+        <v>46148</v>
+      </c>
+      <c r="B127" t="n">
+        <v>0.31895</v>
+      </c>
+      <c r="C127" t="n">
+        <v>0.4245</v>
+      </c>
+      <c r="D127" t="n">
+        <v>0.34074</v>
+      </c>
+      <c r="E127" t="n">
+        <v>0.3455299999999999</v>
+      </c>
+      <c r="F127" t="n">
+        <v>0.33987</v>
+      </c>
+      <c r="G127" t="n">
+        <v>0.33594</v>
+      </c>
+      <c r="H127" t="n">
+        <v>0.32618</v>
+      </c>
+      <c r="I127" t="n">
+        <v>0.32943</v>
+      </c>
+      <c r="J127" t="n">
+        <v>0.32615</v>
+      </c>
+      <c r="K127" t="n">
+        <v>0.32494</v>
+      </c>
+      <c r="L127" t="n">
+        <v>0.32414</v>
+      </c>
+      <c r="M127" t="n">
+        <v>0.3101</v>
+      </c>
+      <c r="N127" t="n">
+        <v>0.32747</v>
+      </c>
+      <c r="O127" t="n">
+        <v>0.32618</v>
+      </c>
+      <c r="P127" t="n">
+        <v>0.31999</v>
+      </c>
+      <c r="Q127" t="n">
+        <v>0.31606</v>
+      </c>
+      <c r="R127" t="n">
+        <v>0.32018</v>
+      </c>
+      <c r="S127" t="n">
+        <v>0.32015</v>
+      </c>
+      <c r="T127" t="n">
+        <v>0.3103</v>
+      </c>
+      <c r="U127" t="n">
+        <v>0.32516</v>
+      </c>
+      <c r="V127" t="n">
+        <v>0.3112799999999999</v>
+      </c>
+      <c r="W127" t="n">
+        <v>0.31923</v>
+      </c>
+      <c r="X127" t="n">
+        <v>0.32053</v>
+      </c>
+      <c r="Y127" t="n">
+        <v>0.39237</v>
+      </c>
+      <c r="Z127" t="n">
+        <v>0.32498</v>
+      </c>
+      <c r="AA127" t="n">
+        <v>0.3499</v>
+      </c>
+      <c r="AB127" t="n">
+        <v>0.39994</v>
+      </c>
+      <c r="AC127" t="n">
+        <v>0.37494</v>
+      </c>
+      <c r="AD127" t="n">
+        <v>0.3499</v>
+      </c>
+      <c r="AE127" t="n">
+        <v>0.33878</v>
+      </c>
+      <c r="AF127" t="n">
+        <v>0.35557</v>
+      </c>
+      <c r="AG127" t="n">
+        <v>0.33215</v>
+      </c>
+      <c r="AH127" t="n">
+        <v>0.33454</v>
+      </c>
+      <c r="AI127" t="n">
+        <v>0.31898</v>
+      </c>
+      <c r="AJ127" t="n">
+        <v>0.27319</v>
+      </c>
+      <c r="AK127" t="n">
+        <v>0.33423</v>
+      </c>
+      <c r="AL127" t="n">
+        <v>0.33718</v>
+      </c>
+      <c r="AM127" t="n">
+        <v>0.30153</v>
+      </c>
+      <c r="AN127" t="n">
+        <v>0.32079</v>
+      </c>
+      <c r="AO127" t="n">
+        <v>0.06609000000000001</v>
+      </c>
+      <c r="AP127" t="n">
+        <v>0.30961</v>
+      </c>
+      <c r="AQ127" t="n">
+        <v>0.2509</v>
+      </c>
+      <c r="AR127" t="n">
+        <v>0.14991</v>
+      </c>
+      <c r="AS127" t="n">
+        <v>0.14912</v>
+      </c>
+      <c r="AT127" t="n">
+        <v>0.31563</v>
+      </c>
+      <c r="AU127" t="n">
+        <v>0.15399</v>
+      </c>
+      <c r="AV127" t="n">
+        <v>0.57386</v>
+      </c>
+      <c r="AW127" t="n">
+        <v>0.60629</v>
+      </c>
+      <c r="AX127" t="n">
+        <v>0.14457</v>
+      </c>
+      <c r="AY127" t="n">
+        <v>0.14501</v>
+      </c>
+      <c r="AZ127" t="n">
+        <v>0.14211</v>
+      </c>
+      <c r="BA127" t="n">
+        <v>0.14893</v>
+      </c>
+      <c r="BB127" t="n">
+        <v>0.27151</v>
+      </c>
+      <c r="BC127" t="n">
+        <v>0.14997</v>
+      </c>
+      <c r="BD127" t="n">
+        <v>0.27808</v>
+      </c>
+      <c r="BE127" t="n">
+        <v>0.28067</v>
+      </c>
+      <c r="BF127" t="n">
+        <v>0.14713</v>
+      </c>
+      <c r="BG127" t="n">
+        <v>0.13191</v>
+      </c>
+      <c r="BH127" t="n">
+        <v>0.11817</v>
+      </c>
+      <c r="BI127" t="n">
+        <v>0.11871</v>
+      </c>
+      <c r="BJ127" t="n">
+        <v>0.17515</v>
+      </c>
+      <c r="BK127" t="n">
+        <v>0.14589</v>
+      </c>
+      <c r="BL127" t="n">
+        <v>0.15383</v>
+      </c>
+      <c r="BM127" t="n">
+        <v>0.30583</v>
+      </c>
+      <c r="BN127" t="n">
+        <v>0.3345</v>
+      </c>
+      <c r="BO127" t="n">
+        <v>0.34183</v>
+      </c>
+      <c r="BP127" t="n">
+        <v>0.33394</v>
+      </c>
+      <c r="BQ127" t="n">
+        <v>0.35274</v>
+      </c>
+      <c r="BR127" t="n">
+        <v>0.31749</v>
+      </c>
+      <c r="BS127" t="n">
+        <v>0.36956</v>
+      </c>
+      <c r="BT127" t="n">
+        <v>0.36203</v>
+      </c>
+      <c r="BU127" t="n">
+        <v>0.40644</v>
+      </c>
+      <c r="BV127" t="n">
+        <v>0.34362</v>
+      </c>
+      <c r="BW127" t="n">
+        <v>0.37991</v>
+      </c>
+      <c r="BX127" t="n">
+        <v>0.34659</v>
+      </c>
+      <c r="BY127" t="n">
+        <v>0.40029</v>
+      </c>
+      <c r="BZ127" t="n">
+        <v>0.36069</v>
+      </c>
+      <c r="CA127" t="n">
+        <v>0.38488</v>
+      </c>
+      <c r="CB127" t="n">
+        <v>0.45042</v>
+      </c>
+      <c r="CC127" t="n">
+        <v>0.40067</v>
+      </c>
+      <c r="CD127" t="n">
+        <v>0.39357</v>
+      </c>
+      <c r="CE127" t="n">
+        <v>0.40184</v>
+      </c>
+      <c r="CF127" t="n">
+        <v>0.39768</v>
+      </c>
+      <c r="CG127" t="n">
+        <v>0.44081</v>
+      </c>
+      <c r="CH127" t="n">
+        <v>0.43987</v>
+      </c>
+      <c r="CI127" t="n">
+        <v>0.43923</v>
+      </c>
+      <c r="CJ127" t="n">
+        <v>0.44416</v>
+      </c>
+      <c r="CK127" t="n">
+        <v>0.44425</v>
+      </c>
+      <c r="CL127" t="n">
+        <v>0.40351</v>
+      </c>
+      <c r="CM127" t="n">
+        <v>0.39144</v>
+      </c>
+      <c r="CN127" t="n">
+        <v>0.39859</v>
+      </c>
+      <c r="CO127" t="n">
+        <v>0.39158</v>
+      </c>
+      <c r="CP127" t="n">
+        <v>0.35971</v>
+      </c>
+      <c r="CQ127" t="n">
+        <v>0.36035</v>
+      </c>
+      <c r="CR127" t="n">
+        <v>0.34801</v>
+      </c>
+      <c r="CS127" t="n">
+        <v>0.34931</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="2" t="n">
+        <v>46149</v>
+      </c>
+      <c r="B128" t="n">
+        <v>0.33967</v>
+      </c>
+      <c r="C128" t="n">
+        <v>0.54243</v>
+      </c>
+      <c r="D128" t="n">
+        <v>0.38954</v>
+      </c>
+      <c r="E128" t="n">
+        <v>0.46864</v>
+      </c>
+      <c r="F128" t="n">
+        <v>0.42382</v>
+      </c>
+      <c r="G128" t="n">
+        <v>0.4159</v>
+      </c>
+      <c r="H128" t="n">
+        <v>0.37012</v>
+      </c>
+      <c r="I128" t="n">
+        <v>0.38105</v>
+      </c>
+      <c r="J128" t="n">
+        <v>0.38017</v>
+      </c>
+      <c r="K128" t="n">
+        <v>0.39365</v>
+      </c>
+      <c r="L128" t="n">
+        <v>0.38144</v>
+      </c>
+      <c r="M128" t="n">
+        <v>0.37115</v>
+      </c>
+      <c r="N128" t="n">
+        <v>0.38148</v>
+      </c>
+      <c r="O128" t="n">
+        <v>0.36134</v>
+      </c>
+      <c r="P128" t="n">
+        <v>0.39234</v>
+      </c>
+      <c r="Q128" t="n">
+        <v>0.3712</v>
+      </c>
+      <c r="R128" t="n">
+        <v>0.38133</v>
+      </c>
+      <c r="S128" t="n">
+        <v>0.35026</v>
+      </c>
+      <c r="T128" t="n">
+        <v>0.34797</v>
+      </c>
+      <c r="U128" t="n">
+        <v>0.35525</v>
+      </c>
+      <c r="V128" t="n">
+        <v>0.34488</v>
+      </c>
+      <c r="W128" t="n">
+        <v>0.34066</v>
+      </c>
+      <c r="X128" t="n">
+        <v>0.34593</v>
+      </c>
+      <c r="Y128" t="n">
+        <v>0.34066</v>
+      </c>
+      <c r="Z128" t="n">
+        <v>0.34601</v>
+      </c>
+      <c r="AA128" t="n">
+        <v>0.35649</v>
+      </c>
+      <c r="AB128" t="n">
+        <v>0.37145</v>
+      </c>
+      <c r="AC128" t="n">
+        <v>0.38125</v>
+      </c>
+      <c r="AD128" t="n">
+        <v>0.36094</v>
+      </c>
+      <c r="AE128" t="n">
+        <v>0.34105</v>
+      </c>
+      <c r="AF128" t="n">
+        <v>0.34116</v>
+      </c>
+      <c r="AG128" t="n">
+        <v>0.34033</v>
+      </c>
+      <c r="AH128" t="n">
+        <v>0.3293</v>
+      </c>
+      <c r="AI128" t="n">
+        <v>0.34358</v>
+      </c>
+      <c r="AJ128" t="n">
+        <v>0.35145</v>
+      </c>
+      <c r="AK128" t="n">
+        <v>0.37504</v>
+      </c>
+      <c r="AL128" t="n">
+        <v>0.28852</v>
+      </c>
+      <c r="AM128" t="n">
+        <v>0.31282</v>
+      </c>
+      <c r="AN128" t="n">
+        <v>0.31245</v>
+      </c>
+      <c r="AO128" t="n">
+        <v>0.30622</v>
+      </c>
+      <c r="AP128" t="n">
+        <v>0.28525</v>
+      </c>
+      <c r="AQ128" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AR128" t="n">
+        <v>-0.04098</v>
+      </c>
+      <c r="AS128" t="n">
+        <v>-0.0347</v>
+      </c>
+      <c r="AT128" t="n">
+        <v>0.23422</v>
+      </c>
+      <c r="AU128" t="n">
+        <v>0.30233</v>
+      </c>
+      <c r="AV128" t="n">
+        <v>0.24411</v>
+      </c>
+      <c r="AW128" t="n">
+        <v>0.23526</v>
+      </c>
+      <c r="AX128" t="n">
+        <v>0.26252</v>
+      </c>
+      <c r="AY128" t="n">
+        <v>0.29741</v>
+      </c>
+      <c r="AZ128" t="n">
+        <v>0.28123</v>
+      </c>
+      <c r="BA128" t="n">
+        <v>0.31256</v>
+      </c>
+      <c r="BB128" t="n">
+        <v>0.28495</v>
+      </c>
+      <c r="BC128" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BD128" t="n">
+        <v>0.25477</v>
+      </c>
+      <c r="BE128" t="n">
+        <v>0.30227</v>
+      </c>
+      <c r="BF128" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BG128" t="n">
+        <v>0.27207</v>
+      </c>
+      <c r="BH128" t="n">
+        <v>0.22827</v>
+      </c>
+      <c r="BI128" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BJ128" t="n">
+        <v>0.28829</v>
+      </c>
+      <c r="BK128" t="n">
+        <v>0.28863</v>
+      </c>
+      <c r="BL128" t="n">
+        <v>0.29481</v>
+      </c>
+      <c r="BM128" t="n">
+        <v>0.27347</v>
+      </c>
+      <c r="BN128" t="n">
+        <v>0.30895</v>
+      </c>
+      <c r="BO128" t="n">
+        <v>0.32036</v>
+      </c>
+      <c r="BP128" t="n">
+        <v>0.3289</v>
+      </c>
+      <c r="BQ128" t="n">
+        <v>0.31125</v>
+      </c>
+      <c r="BR128" t="n">
+        <v>0.29022</v>
+      </c>
+      <c r="BS128" t="n">
+        <v>0.2554</v>
+      </c>
+      <c r="BT128" t="n">
+        <v>0.2704</v>
+      </c>
+      <c r="BU128" t="n">
+        <v>0.30243</v>
+      </c>
+      <c r="BV128" t="n">
+        <v>0.34519</v>
+      </c>
+      <c r="BW128" t="n">
+        <v>0.34429</v>
+      </c>
+      <c r="BX128" t="n">
+        <v>0.35682</v>
+      </c>
+      <c r="BY128" t="n">
+        <v>0.3455299999999999</v>
+      </c>
+      <c r="BZ128" t="n">
+        <v>0.31486</v>
+      </c>
+      <c r="CA128" t="n">
+        <v>0.30088</v>
+      </c>
+      <c r="CB128" t="n">
+        <v>0.32773</v>
+      </c>
+      <c r="CC128" t="n">
+        <v>0.18776</v>
+      </c>
+      <c r="CD128" t="n">
+        <v>0.34193</v>
+      </c>
+      <c r="CE128" t="n">
+        <v>0.3779</v>
+      </c>
+      <c r="CF128" t="n">
+        <v>0.35036</v>
+      </c>
+      <c r="CG128" t="n">
+        <v>0.35452</v>
+      </c>
+      <c r="CH128" t="n">
+        <v>0.35323</v>
+      </c>
+      <c r="CI128" t="n">
+        <v>0.41958</v>
+      </c>
+      <c r="CJ128" t="n">
+        <v>0.38981</v>
+      </c>
+      <c r="CK128" t="n">
+        <v>0.33967</v>
+      </c>
+      <c r="CL128" t="n">
+        <v>0.36496</v>
+      </c>
+      <c r="CM128" t="n">
+        <v>0.36839</v>
+      </c>
+      <c r="CN128" t="n">
+        <v>0.35827</v>
+      </c>
+      <c r="CO128" t="n">
+        <v>0.38028</v>
+      </c>
+      <c r="CP128" t="n">
+        <v>0.38035</v>
+      </c>
+      <c r="CQ128" t="n">
+        <v>0.3853</v>
+      </c>
+      <c r="CR128" t="n">
+        <v>0.34998</v>
+      </c>
+      <c r="CS128" t="n">
+        <v>0.36024</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="2" t="n">
+        <v>46150</v>
+      </c>
+      <c r="B129" t="n">
+        <v>0.3402</v>
+      </c>
+      <c r="C129" t="n">
+        <v>0.36615</v>
+      </c>
+      <c r="D129" t="n">
+        <v>0.41893</v>
+      </c>
+      <c r="E129" t="n">
+        <v>0.37072</v>
+      </c>
+      <c r="F129" t="n">
+        <v>0.39</v>
+      </c>
+      <c r="G129" t="n">
+        <v>0.38059</v>
+      </c>
+      <c r="H129" t="n">
+        <v>0.35281</v>
+      </c>
+      <c r="I129" t="n">
+        <v>0.34956</v>
+      </c>
+      <c r="J129" t="n">
+        <v>0.36031</v>
+      </c>
+      <c r="K129" t="n">
+        <v>0.35181</v>
+      </c>
+      <c r="L129" t="n">
+        <v>0.34204</v>
+      </c>
+      <c r="M129" t="n">
+        <v>0.34783</v>
+      </c>
+      <c r="N129" t="n">
+        <v>0.34584</v>
+      </c>
+      <c r="O129" t="n">
+        <v>0.35006</v>
+      </c>
+      <c r="P129" t="n">
+        <v>0.34721</v>
+      </c>
+      <c r="Q129" t="n">
+        <v>0.35007</v>
+      </c>
+      <c r="R129" t="n">
+        <v>0.34092</v>
+      </c>
+      <c r="S129" t="n">
+        <v>0.34262</v>
+      </c>
+      <c r="T129" t="n">
+        <v>0.3434</v>
+      </c>
+      <c r="U129" t="n">
+        <v>0.33888</v>
+      </c>
+      <c r="V129" t="n">
+        <v>0.33856</v>
+      </c>
+      <c r="W129" t="n">
+        <v>0.33994</v>
+      </c>
+      <c r="X129" t="n">
+        <v>0.3307</v>
+      </c>
+      <c r="Y129" t="n">
+        <v>0.34119</v>
+      </c>
+      <c r="Z129" t="n">
+        <v>0.3322</v>
+      </c>
+      <c r="AA129" t="n">
+        <v>0.35068</v>
+      </c>
+      <c r="AB129" t="n">
+        <v>0.34411</v>
+      </c>
+      <c r="AC129" t="n">
+        <v>0.36097</v>
+      </c>
+      <c r="AD129" t="n">
+        <v>0.31252</v>
+      </c>
+      <c r="AE129" t="n">
+        <v>0.32637</v>
+      </c>
+      <c r="AF129" t="n">
+        <v>0.33926</v>
+      </c>
+      <c r="AG129" t="n">
+        <v>0.32481</v>
+      </c>
+      <c r="AH129" t="n">
+        <v>0.31286</v>
+      </c>
+      <c r="AI129" t="n">
+        <v>0.32613</v>
+      </c>
+      <c r="AJ129" t="n">
+        <v>0.31487</v>
+      </c>
+      <c r="AK129" t="n">
+        <v>0.31443</v>
+      </c>
+      <c r="AL129" t="n">
+        <v>0.34975</v>
+      </c>
+      <c r="AM129" t="n">
+        <v>0.32622</v>
+      </c>
+      <c r="AN129" t="n">
+        <v>0.27886</v>
+      </c>
+      <c r="AO129" t="n">
+        <v>0.36667</v>
+      </c>
+      <c r="AP129" t="n">
+        <v>0.39975</v>
+      </c>
+      <c r="AQ129" t="n">
+        <v>0.29403</v>
+      </c>
+      <c r="AR129" t="n">
+        <v>0.38326</v>
+      </c>
+      <c r="AS129" t="n">
+        <v>0.2653</v>
+      </c>
+      <c r="AT129" t="n">
+        <v>0.25815</v>
+      </c>
+      <c r="AU129" t="n">
+        <v>0.32509</v>
+      </c>
+      <c r="AV129" t="n">
+        <v>-0.04589</v>
+      </c>
+      <c r="AW129" t="n">
+        <v>0.2433</v>
+      </c>
+      <c r="AX129" t="n">
+        <v>0.24917</v>
+      </c>
+      <c r="AY129" t="n">
+        <v>0.19511</v>
+      </c>
+      <c r="AZ129" t="n">
+        <v>0.07318000000000001</v>
+      </c>
+      <c r="BA129" t="n">
+        <v>0.17375</v>
+      </c>
+      <c r="BB129" t="n">
+        <v>0.24232</v>
+      </c>
+      <c r="BC129" t="n">
+        <v>0.28068</v>
+      </c>
+      <c r="BD129" t="n">
+        <v>0.30757</v>
+      </c>
+      <c r="BE129" t="n">
+        <v>0.25807</v>
+      </c>
+      <c r="BF129" t="n">
+        <v>0.24091</v>
+      </c>
+      <c r="BG129" t="n">
+        <v>0.27517</v>
+      </c>
+      <c r="BH129" t="n">
+        <v>0.28861</v>
+      </c>
+      <c r="BI129" t="n">
+        <v>0.28354</v>
+      </c>
+      <c r="BJ129" t="n">
+        <v>0.26006</v>
+      </c>
+      <c r="BK129" t="n">
+        <v>0.28464</v>
+      </c>
+      <c r="BL129" t="n">
+        <v>0.32354</v>
+      </c>
+      <c r="BM129" t="n">
+        <v>0.31705</v>
+      </c>
+      <c r="BN129" t="n">
+        <v>0.30894</v>
+      </c>
+      <c r="BO129" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="BP129" t="n">
+        <v>0.31981</v>
+      </c>
+      <c r="BQ129" t="n">
+        <v>0.3153</v>
+      </c>
+      <c r="BR129" t="n">
+        <v>0.3232</v>
+      </c>
+      <c r="BS129" t="n">
+        <v>0.33153</v>
+      </c>
+      <c r="BT129" t="n">
+        <v>0.29258</v>
+      </c>
+      <c r="BU129" t="n">
+        <v>0.36586</v>
+      </c>
+      <c r="BV129" t="n">
+        <v>0.30419</v>
+      </c>
+      <c r="BW129" t="n">
+        <v>0.30804</v>
+      </c>
+      <c r="BX129" t="n">
+        <v>0.30918</v>
+      </c>
+      <c r="BY129" t="n">
+        <v>0.31781</v>
+      </c>
+      <c r="BZ129" t="n">
+        <v>0.31123</v>
+      </c>
+      <c r="CA129" t="n">
+        <v>0.47297</v>
+      </c>
+      <c r="CB129" t="n">
+        <v>0.39138</v>
+      </c>
+      <c r="CC129" t="n">
+        <v>0.71165</v>
+      </c>
+      <c r="CD129" t="n">
+        <v>0.34146</v>
+      </c>
+      <c r="CE129" t="n">
+        <v>0.38744</v>
+      </c>
+      <c r="CF129" t="n">
+        <v>0.33889</v>
+      </c>
+      <c r="CG129" t="n">
+        <v>0.32527</v>
+      </c>
+      <c r="CH129" t="n">
+        <v>0.33433</v>
+      </c>
+      <c r="CI129" t="n">
+        <v>0.36333</v>
+      </c>
+      <c r="CJ129" t="n">
+        <v>0.33269</v>
+      </c>
+      <c r="CK129" t="n">
+        <v>0.40935</v>
+      </c>
+      <c r="CL129" t="n">
+        <v>0.26719</v>
+      </c>
+      <c r="CM129" t="n">
+        <v>0.3375</v>
+      </c>
+      <c r="CN129" t="n">
+        <v>0.34181</v>
+      </c>
+      <c r="CO129" t="n">
+        <v>0.3411</v>
+      </c>
+      <c r="CP129" t="n">
+        <v>0.31419</v>
+      </c>
+      <c r="CQ129" t="n">
+        <v>0.30968</v>
+      </c>
+      <c r="CR129" t="n">
+        <v>0.31437</v>
+      </c>
+      <c r="CS129" t="n">
+        <v>0.29745</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="2" t="n">
+        <v>46151</v>
+      </c>
+      <c r="B130" t="n">
+        <v>0.33472</v>
+      </c>
+      <c r="C130" t="n">
+        <v>0.30493</v>
+      </c>
+      <c r="D130" t="n">
+        <v>0.3474100000000001</v>
+      </c>
+      <c r="E130" t="n">
+        <v>0.32525</v>
+      </c>
+      <c r="F130" t="n">
+        <v>0.32813</v>
+      </c>
+      <c r="G130" t="n">
+        <v>0.32549</v>
+      </c>
+      <c r="H130" t="n">
+        <v>0.33005</v>
+      </c>
+      <c r="I130" t="n">
+        <v>0.32448</v>
+      </c>
+      <c r="J130" t="n">
+        <v>0.325</v>
+      </c>
+      <c r="K130" t="n">
+        <v>0.32324</v>
+      </c>
+      <c r="L130" t="n">
+        <v>0.32368</v>
+      </c>
+      <c r="M130" t="n">
+        <v>0.32624</v>
+      </c>
+      <c r="N130" t="n">
+        <v>0.32476</v>
+      </c>
+      <c r="O130" t="n">
+        <v>0.32761</v>
+      </c>
+      <c r="P130" t="n">
+        <v>0.32896</v>
+      </c>
+      <c r="Q130" t="n">
+        <v>0.32748</v>
+      </c>
+      <c r="R130" t="n">
+        <v>0.32754</v>
+      </c>
+      <c r="S130" t="n">
+        <v>0.32405</v>
+      </c>
+      <c r="T130" t="n">
+        <v>0.33108</v>
+      </c>
+      <c r="U130" t="n">
+        <v>0.32619</v>
+      </c>
+      <c r="V130" t="n">
+        <v>0.32096</v>
+      </c>
+      <c r="W130" t="n">
+        <v>0.31981</v>
+      </c>
+      <c r="X130" t="n">
+        <v>0.32307</v>
+      </c>
+      <c r="Y130" t="n">
+        <v>0.32643</v>
+      </c>
+      <c r="Z130" t="n">
+        <v>0.33113</v>
+      </c>
+      <c r="AA130" t="n">
+        <v>0.33525</v>
+      </c>
+      <c r="AB130" t="n">
+        <v>0.34607</v>
+      </c>
+      <c r="AC130" t="n">
+        <v>0.34082</v>
+      </c>
+      <c r="AD130" t="n">
+        <v>0.34082</v>
+      </c>
+      <c r="AE130" t="n">
+        <v>0.33524</v>
+      </c>
+      <c r="AF130" t="n">
+        <v>0.33881</v>
+      </c>
+      <c r="AG130" t="n">
+        <v>0.32113</v>
+      </c>
+      <c r="AH130" t="n">
+        <v>0.32082</v>
+      </c>
+      <c r="AI130" t="n">
+        <v>0.33431</v>
+      </c>
+      <c r="AJ130" t="n">
+        <v>0.34589</v>
+      </c>
+      <c r="AK130" t="n">
+        <v>0.35036</v>
+      </c>
+      <c r="AL130" t="n">
+        <v>0.33424</v>
+      </c>
+      <c r="AM130" t="n">
+        <v>0.32414</v>
+      </c>
+      <c r="AN130" t="n">
+        <v>0.31485</v>
+      </c>
+      <c r="AO130" t="n">
+        <v>0.31529</v>
+      </c>
+      <c r="AP130" t="n">
+        <v>0.32191</v>
+      </c>
+      <c r="AQ130" t="n">
+        <v>0.31427</v>
+      </c>
+      <c r="AR130" t="n">
+        <v>0.33746</v>
+      </c>
+      <c r="AS130" t="n">
+        <v>0.27976</v>
+      </c>
+      <c r="AT130" t="n">
+        <v>0.34156</v>
+      </c>
+      <c r="AU130" t="n">
+        <v>0.34088</v>
+      </c>
+      <c r="AV130" t="n">
+        <v>0.29114</v>
+      </c>
+      <c r="AW130" t="n">
+        <v>0.32441</v>
+      </c>
+      <c r="AX130" t="n">
+        <v>0.28067</v>
+      </c>
+      <c r="AY130" t="n">
+        <v>0.32465</v>
+      </c>
+      <c r="AZ130" t="n">
+        <v>0.3183</v>
+      </c>
+      <c r="BA130" t="n">
+        <v>0.31961</v>
+      </c>
+      <c r="BB130" t="n">
+        <v>0.32545</v>
+      </c>
+      <c r="BC130" t="n">
+        <v>0.32852</v>
+      </c>
+      <c r="BD130" t="n">
+        <v>0.33328</v>
+      </c>
+      <c r="BE130" t="n">
+        <v>0.33086</v>
+      </c>
+      <c r="BF130" t="n">
+        <v>0.30334</v>
+      </c>
+      <c r="BG130" t="n">
+        <v>0.32655</v>
+      </c>
+      <c r="BH130" t="n">
+        <v>0.31941</v>
+      </c>
+      <c r="BI130" t="n">
+        <v>0.3198</v>
+      </c>
+      <c r="BJ130" t="n">
+        <v>0.31986</v>
+      </c>
+      <c r="BK130" t="n">
+        <v>0.31295</v>
+      </c>
+      <c r="BL130" t="n">
+        <v>0.34834</v>
+      </c>
+      <c r="BM130" t="n">
+        <v>0.29953</v>
+      </c>
+      <c r="BN130" t="n">
+        <v>0.2785899999999999</v>
+      </c>
+      <c r="BO130" t="n">
+        <v>0.30886</v>
+      </c>
+      <c r="BP130" t="n">
+        <v>0.34154</v>
+      </c>
+      <c r="BQ130" t="n">
+        <v>0.32162</v>
+      </c>
+      <c r="BR130" t="n">
+        <v>0.3403</v>
+      </c>
+      <c r="BS130" t="n">
+        <v>0.33131</v>
+      </c>
+      <c r="BT130" t="n">
+        <v>0.35006</v>
+      </c>
+      <c r="BU130" t="n">
+        <v>0.35008</v>
+      </c>
+      <c r="BV130" t="n">
+        <v>0.35009</v>
+      </c>
+      <c r="BW130" t="n">
+        <v>0.35914</v>
+      </c>
+      <c r="BX130" t="n">
+        <v>0.32566</v>
+      </c>
+      <c r="BY130" t="n">
+        <v>0.32803</v>
+      </c>
+      <c r="BZ130" t="n">
+        <v>0.34619</v>
+      </c>
+      <c r="CA130" t="n">
+        <v>0.37551</v>
+      </c>
+      <c r="CB130" t="n">
+        <v>0.36792</v>
+      </c>
+      <c r="CC130" t="n">
+        <v>0.36197</v>
+      </c>
+      <c r="CD130" t="n">
+        <v>0.36829</v>
+      </c>
+      <c r="CE130" t="n">
+        <v>0.36287</v>
+      </c>
+      <c r="CF130" t="n">
+        <v>0.37358</v>
+      </c>
+      <c r="CG130" t="n">
+        <v>0.36221</v>
+      </c>
+      <c r="CH130" t="n">
+        <v>0.39363</v>
+      </c>
+      <c r="CI130" t="n">
+        <v>0.38557</v>
+      </c>
+      <c r="CJ130" t="n">
+        <v>0.37164</v>
+      </c>
+      <c r="CK130" t="n">
+        <v>0.40321</v>
+      </c>
+      <c r="CL130" t="n">
+        <v>0.355</v>
+      </c>
+      <c r="CM130" t="n">
+        <v>0.38008</v>
+      </c>
+      <c r="CN130" t="n">
+        <v>0.36994</v>
+      </c>
+      <c r="CO130" t="n">
+        <v>0.36102</v>
+      </c>
+      <c r="CP130" t="n">
+        <v>0.35032</v>
+      </c>
+      <c r="CQ130" t="n">
+        <v>0.35005</v>
+      </c>
+      <c r="CR130" t="n">
+        <v>0.34947</v>
+      </c>
+      <c r="CS130" t="n">
+        <v>0.34923</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="2" t="n">
+        <v>46152</v>
+      </c>
+      <c r="B131" t="n">
+        <v>0.33964</v>
+      </c>
+      <c r="C131" t="n">
+        <v>0.35145</v>
+      </c>
+      <c r="D131" t="n">
+        <v>0.35591</v>
+      </c>
+      <c r="E131" t="n">
+        <v>0.35586</v>
+      </c>
+      <c r="F131" t="n">
+        <v>0.35144</v>
+      </c>
+      <c r="G131" t="n">
+        <v>0.35085</v>
+      </c>
+      <c r="H131" t="n">
+        <v>0.35005</v>
+      </c>
+      <c r="I131" t="n">
+        <v>0.34953</v>
+      </c>
+      <c r="J131" t="n">
+        <v>0.34947</v>
+      </c>
+      <c r="K131" t="n">
+        <v>0.34631</v>
+      </c>
+      <c r="L131" t="n">
+        <v>0.36006</v>
+      </c>
+      <c r="M131" t="n">
+        <v>0.34711</v>
+      </c>
+      <c r="N131" t="n">
+        <v>0.34986</v>
+      </c>
+      <c r="O131" t="n">
+        <v>0.34956</v>
+      </c>
+      <c r="P131" t="n">
+        <v>0.33706</v>
+      </c>
+      <c r="Q131" t="n">
+        <v>0.33964</v>
+      </c>
+      <c r="R131" t="n">
+        <v>0.34005</v>
+      </c>
+      <c r="S131" t="n">
+        <v>0.33968</v>
+      </c>
+      <c r="T131" t="n">
+        <v>0.36943</v>
+      </c>
+      <c r="U131" t="n">
+        <v>0.32439</v>
+      </c>
+      <c r="V131" t="n">
+        <v>0.33839</v>
+      </c>
+      <c r="W131" t="n">
+        <v>0.33964</v>
+      </c>
+      <c r="X131" t="n">
+        <v>0.34956</v>
+      </c>
+      <c r="Y131" t="n">
+        <v>0.33674</v>
+      </c>
+      <c r="Z131" t="n">
+        <v>0.3397</v>
+      </c>
+      <c r="AA131" t="n">
+        <v>0.34505</v>
+      </c>
+      <c r="AB131" t="n">
+        <v>0.33595</v>
+      </c>
+      <c r="AC131" t="n">
+        <v>0.34955</v>
+      </c>
+      <c r="AD131" t="n">
+        <v>0.34955</v>
+      </c>
+      <c r="AE131" t="n">
+        <v>0.33638</v>
+      </c>
+      <c r="AF131" t="n">
+        <v>0.34013</v>
+      </c>
+      <c r="AG131" t="n">
+        <v>0.32814</v>
+      </c>
+      <c r="AH131" t="n">
+        <v>0.34862</v>
+      </c>
+      <c r="AI131" t="n">
+        <v>0.3394</v>
+      </c>
+      <c r="AJ131" t="n">
+        <v>0.33149</v>
+      </c>
+      <c r="AK131" t="n">
+        <v>0.33556</v>
+      </c>
+      <c r="AL131" t="n">
+        <v>0.28306</v>
+      </c>
+      <c r="AM131" t="n">
+        <v>0.3261</v>
+      </c>
+      <c r="AN131" t="n">
+        <v>0.32753</v>
+      </c>
+      <c r="AO131" t="n">
+        <v>0.32887</v>
+      </c>
+      <c r="AP131" t="n">
+        <v>0.3253</v>
+      </c>
+      <c r="AQ131" t="n">
+        <v>0.31833</v>
+      </c>
+      <c r="AR131" t="n">
+        <v>0.32693</v>
+      </c>
+      <c r="AS131" t="n">
+        <v>0.31754</v>
+      </c>
+      <c r="AT131" t="n">
+        <v>0.31797</v>
+      </c>
+      <c r="AU131" t="n">
+        <v>0.32716</v>
+      </c>
+      <c r="AV131" t="n">
+        <v>0.32476</v>
+      </c>
+      <c r="AW131" t="n">
+        <v>0.32815</v>
+      </c>
+      <c r="AX131" t="n">
+        <v>0.31885</v>
+      </c>
+      <c r="AY131" t="n">
+        <v>0.37046</v>
+      </c>
+      <c r="AZ131" t="n">
+        <v>0.32395</v>
+      </c>
+      <c r="BA131" t="n">
+        <v>0.31928</v>
+      </c>
+      <c r="BB131" t="n">
+        <v>0.31492</v>
+      </c>
+      <c r="BC131" t="n">
+        <v>0.31526</v>
+      </c>
+      <c r="BD131" t="n">
+        <v>0.32224</v>
+      </c>
+      <c r="BE131" t="n">
+        <v>0.31197</v>
+      </c>
+      <c r="BF131" t="n">
+        <v>0.32615</v>
+      </c>
+      <c r="BG131" t="n">
+        <v>0.32077</v>
+      </c>
+      <c r="BH131" t="n">
+        <v>0.3221</v>
+      </c>
+      <c r="BI131" t="n">
+        <v>0.32892</v>
+      </c>
+      <c r="BJ131" t="n">
+        <v>0.32987</v>
+      </c>
+      <c r="BK131" t="n">
+        <v>0.33176</v>
+      </c>
+      <c r="BL131" t="n">
+        <v>0.336</v>
+      </c>
+      <c r="BM131" t="n">
+        <v>0.34564</v>
+      </c>
+      <c r="BN131" t="n">
+        <v>0.35791</v>
+      </c>
+      <c r="BO131" t="n">
+        <v>0.5754400000000001</v>
+      </c>
+      <c r="BP131" t="n">
+        <v>0.3911</v>
+      </c>
+      <c r="BQ131" t="n">
+        <v>0.35465</v>
+      </c>
+      <c r="BR131" t="n">
+        <v>0.35462</v>
+      </c>
+      <c r="BS131" t="n">
+        <v>0.36578</v>
+      </c>
+      <c r="BT131" t="n">
+        <v>0.35046</v>
+      </c>
+      <c r="BU131" t="n">
+        <v>0.35983</v>
+      </c>
+      <c r="BV131" t="n">
+        <v>0.34723</v>
+      </c>
+      <c r="BW131" t="n">
+        <v>0.36038</v>
+      </c>
+      <c r="BX131" t="n">
+        <v>0.36031</v>
+      </c>
+      <c r="BY131" t="n">
+        <v>0.36234</v>
+      </c>
+      <c r="BZ131" t="n">
+        <v>0.35028</v>
+      </c>
+      <c r="CA131" t="n">
+        <v>0.3767200000000001</v>
+      </c>
+      <c r="CB131" t="n">
+        <v>0.37968</v>
+      </c>
+      <c r="CC131" t="n">
+        <v>0.38084</v>
+      </c>
+      <c r="CD131" t="n">
+        <v>0.38351</v>
+      </c>
+      <c r="CE131" t="n">
+        <v>0.42964</v>
+      </c>
+      <c r="CF131" t="n">
+        <v>0.40897</v>
+      </c>
+      <c r="CG131" t="n">
+        <v>0.38601</v>
+      </c>
+      <c r="CH131" t="n">
+        <v>0.38552</v>
+      </c>
+      <c r="CI131" t="n">
+        <v>0.65135</v>
+      </c>
+      <c r="CJ131" t="n">
+        <v>0.83335</v>
+      </c>
+      <c r="CK131" t="n">
+        <v>0.47284</v>
+      </c>
+      <c r="CL131" t="n">
+        <v>0.40729</v>
+      </c>
+      <c r="CM131" t="n">
+        <v>0.45936</v>
+      </c>
+      <c r="CN131" t="n">
+        <v>0.39338</v>
+      </c>
+      <c r="CO131" t="n">
+        <v>0.35073</v>
+      </c>
+      <c r="CP131" t="n">
+        <v>0.35094</v>
+      </c>
+      <c r="CQ131" t="n">
+        <v>0.35965</v>
+      </c>
+      <c r="CR131" t="n">
+        <v>0.33992</v>
+      </c>
+      <c r="CS131" t="n">
+        <v>0.34483</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="2" t="n">
+        <v>46154</v>
+      </c>
+      <c r="B132" t="n">
+        <v>0.31389</v>
+      </c>
+      <c r="C132" t="n">
+        <v>0.41156</v>
+      </c>
+      <c r="D132" t="n">
+        <v>0.37664</v>
+      </c>
+      <c r="E132" t="n">
+        <v>0.37174</v>
+      </c>
+      <c r="F132" t="n">
+        <v>0.36394</v>
+      </c>
+      <c r="G132" t="n">
+        <v>0.36005</v>
+      </c>
+      <c r="H132" t="n">
+        <v>0.35982</v>
+      </c>
+      <c r="I132" t="n">
+        <v>0.36287</v>
+      </c>
+      <c r="J132" t="n">
+        <v>0.3593</v>
+      </c>
+      <c r="K132" t="n">
+        <v>0.36097</v>
+      </c>
+      <c r="L132" t="n">
+        <v>0.3598</v>
+      </c>
+      <c r="M132" t="n">
+        <v>0.35363</v>
+      </c>
+      <c r="N132" t="n">
+        <v>0.36067</v>
+      </c>
+      <c r="O132" t="n">
+        <v>0.36084</v>
+      </c>
+      <c r="P132" t="n">
+        <v>0.35685</v>
+      </c>
+      <c r="Q132" t="n">
+        <v>0.35238</v>
+      </c>
+      <c r="R132" t="n">
+        <v>0.35981</v>
+      </c>
+      <c r="S132" t="n">
+        <v>0.36015</v>
+      </c>
+      <c r="T132" t="n">
+        <v>0.35981</v>
+      </c>
+      <c r="U132" t="n">
+        <v>0.34076</v>
+      </c>
+      <c r="V132" t="n">
+        <v>0.37089</v>
+      </c>
+      <c r="W132" t="n">
+        <v>0.3588</v>
+      </c>
+      <c r="X132" t="n">
+        <v>0.35651</v>
+      </c>
+      <c r="Y132" t="n">
+        <v>0.36009</v>
+      </c>
+      <c r="Z132" t="n">
+        <v>0.36009</v>
+      </c>
+      <c r="AA132" t="n">
+        <v>0.37954</v>
+      </c>
+      <c r="AB132" t="n">
+        <v>0.36588</v>
+      </c>
+      <c r="AC132" t="n">
+        <v>0.3799</v>
+      </c>
+      <c r="AD132" t="n">
+        <v>0.35654</v>
+      </c>
+      <c r="AE132" t="n">
+        <v>0.3565</v>
+      </c>
+      <c r="AF132" t="n">
+        <v>0.35114</v>
+      </c>
+      <c r="AG132" t="n">
+        <v>0.35183</v>
+      </c>
+      <c r="AH132" t="n">
+        <v>0.35822</v>
+      </c>
+      <c r="AI132" t="n">
+        <v>0.34978</v>
+      </c>
+      <c r="AJ132" t="n">
+        <v>0.32991</v>
+      </c>
+      <c r="AK132" t="n">
+        <v>0.31982</v>
+      </c>
+      <c r="AL132" t="n">
+        <v>0.33167</v>
+      </c>
+      <c r="AM132" t="n">
+        <v>0.32196</v>
+      </c>
+      <c r="AN132" t="n">
+        <v>0.26084</v>
+      </c>
+      <c r="AO132" t="n">
+        <v>0.13388</v>
+      </c>
+      <c r="AP132" t="n">
+        <v>0.29133</v>
+      </c>
+      <c r="AQ132" t="n">
+        <v>0.28408</v>
+      </c>
+      <c r="AR132" t="n">
+        <v>0.28269</v>
+      </c>
+      <c r="AS132" t="n">
+        <v>0.19533</v>
+      </c>
+      <c r="AT132" t="n">
+        <v>0.24628</v>
+      </c>
+      <c r="AU132" t="n">
+        <v>0.27865</v>
+      </c>
+      <c r="AV132" t="n">
+        <v>-0.04806000000000001</v>
+      </c>
+      <c r="AW132" t="n">
+        <v>0.27938</v>
+      </c>
+      <c r="AX132" t="n">
+        <v>0.12456</v>
+      </c>
+      <c r="AY132" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AZ132" t="n">
+        <v>0.28349</v>
+      </c>
+      <c r="BA132" t="n">
+        <v>0.22547</v>
+      </c>
+      <c r="BB132" t="n">
+        <v>0.28661</v>
+      </c>
+      <c r="BC132" t="n">
+        <v>0.23698</v>
+      </c>
+      <c r="BD132" t="n">
+        <v>0.30336</v>
+      </c>
+      <c r="BE132" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BF132" t="n">
+        <v>0.30176</v>
+      </c>
+      <c r="BG132" t="n">
+        <v>0.1435</v>
+      </c>
+      <c r="BH132" t="n">
+        <v>0.29581</v>
+      </c>
+      <c r="BI132" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BJ132" t="n">
+        <v>0.19718</v>
+      </c>
+      <c r="BK132" t="n">
+        <v>0.20634</v>
+      </c>
+      <c r="BL132" t="n">
+        <v>0.27704</v>
+      </c>
+      <c r="BM132" t="n">
+        <v>0.27993</v>
+      </c>
+      <c r="BN132" t="n">
+        <v>0.29587</v>
+      </c>
+      <c r="BO132" t="n">
+        <v>0.29057</v>
+      </c>
+      <c r="BP132" t="n">
+        <v>0.30466</v>
+      </c>
+      <c r="BQ132" t="n">
+        <v>0.28449</v>
+      </c>
+      <c r="BR132" t="n">
+        <v>0.31174</v>
+      </c>
+      <c r="BS132" t="n">
+        <v>0.3147799999999999</v>
+      </c>
+      <c r="BT132" t="n">
+        <v>0.3324</v>
+      </c>
+      <c r="BU132" t="n">
+        <v>0.33292</v>
+      </c>
+      <c r="BV132" t="n">
+        <v>0.29626</v>
+      </c>
+      <c r="BW132" t="n">
+        <v>0.33427</v>
+      </c>
+      <c r="BX132" t="n">
+        <v>0.40631</v>
+      </c>
+      <c r="BY132" t="n">
+        <v>0.35675</v>
+      </c>
+      <c r="BZ132" t="n">
+        <v>0.39599</v>
+      </c>
+      <c r="CA132" t="n">
+        <v>0.6381</v>
+      </c>
+      <c r="CB132" t="n">
+        <v>0.60375</v>
+      </c>
+      <c r="CC132" t="n">
+        <v>0.5952999999999999</v>
+      </c>
+      <c r="CD132" t="n">
+        <v>0.45775</v>
+      </c>
+      <c r="CE132" t="n">
+        <v>0.6253</v>
+      </c>
+      <c r="CF132" t="n">
+        <v>0.45676</v>
+      </c>
+      <c r="CG132" t="n">
+        <v>0.37663</v>
+      </c>
+      <c r="CH132" t="n">
+        <v>0.43111</v>
+      </c>
+      <c r="CI132" t="n">
+        <v>0.45297</v>
+      </c>
+      <c r="CJ132" t="n">
+        <v>0.3983</v>
+      </c>
+      <c r="CK132" t="n">
+        <v>0.37337</v>
+      </c>
+      <c r="CL132" t="n">
+        <v>0.35407</v>
+      </c>
+      <c r="CM132" t="n">
+        <v>0.47801</v>
+      </c>
+      <c r="CN132" t="n">
+        <v>0.43067</v>
+      </c>
+      <c r="CO132" t="n">
+        <v>0.41969</v>
+      </c>
+      <c r="CP132" t="n">
+        <v>0.3791</v>
+      </c>
+      <c r="CQ132" t="n">
+        <v>0.37506</v>
+      </c>
+      <c r="CR132" t="n">
+        <v>0.36732</v>
+      </c>
+      <c r="CS132" t="n">
+        <v>0.36017</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="2" t="n">
+        <v>46156</v>
+      </c>
+      <c r="B133" t="n">
+        <v>0.3455</v>
+      </c>
+      <c r="C133" t="n">
+        <v>0.49022</v>
+      </c>
+      <c r="D133" t="n">
+        <v>0.40165</v>
+      </c>
+      <c r="E133" t="n">
+        <v>0.42506</v>
+      </c>
+      <c r="F133" t="n">
+        <v>0.43307</v>
+      </c>
+      <c r="G133" t="n">
+        <v>0.41954</v>
+      </c>
+      <c r="H133" t="n">
+        <v>0.39941</v>
+      </c>
+      <c r="I133" t="n">
+        <v>0.40582</v>
+      </c>
+      <c r="J133" t="n">
+        <v>0.41281</v>
+      </c>
+      <c r="K133" t="n">
+        <v>0.41044</v>
+      </c>
+      <c r="L133" t="n">
+        <v>0.41856</v>
+      </c>
+      <c r="M133" t="n">
+        <v>0.40088</v>
+      </c>
+      <c r="N133" t="n">
+        <v>0.39718</v>
+      </c>
+      <c r="O133" t="n">
+        <v>0.41293</v>
+      </c>
+      <c r="P133" t="n">
+        <v>0.41065</v>
+      </c>
+      <c r="Q133" t="n">
+        <v>0.39447</v>
+      </c>
+      <c r="R133" t="n">
+        <v>0.38843</v>
+      </c>
+      <c r="S133" t="n">
+        <v>0.41919</v>
+      </c>
+      <c r="T133" t="n">
+        <v>0.38852</v>
+      </c>
+      <c r="U133" t="n">
+        <v>0.41719</v>
+      </c>
+      <c r="V133" t="n">
+        <v>0.39055</v>
+      </c>
+      <c r="W133" t="n">
+        <v>0.40037</v>
+      </c>
+      <c r="X133" t="n">
+        <v>0.40033</v>
+      </c>
+      <c r="Y133" t="n">
+        <v>0.41307</v>
+      </c>
+      <c r="Z133" t="n">
+        <v>0.40012</v>
+      </c>
+      <c r="AA133" t="n">
+        <v>0.45074</v>
+      </c>
+      <c r="AB133" t="n">
+        <v>0.44951</v>
+      </c>
+      <c r="AC133" t="n">
+        <v>0.56086</v>
+      </c>
+      <c r="AD133" t="n">
+        <v>0.5007699999999999</v>
+      </c>
+      <c r="AE133" t="n">
+        <v>0.45091</v>
+      </c>
+      <c r="AF133" t="n">
+        <v>0.31653</v>
+      </c>
+      <c r="AG133" t="n">
+        <v>0.40969</v>
+      </c>
+      <c r="AH133" t="n">
+        <v>0.21454</v>
+      </c>
+      <c r="AI133" t="n">
+        <v>0.30515</v>
+      </c>
+      <c r="AJ133" t="n">
+        <v>0.38129</v>
+      </c>
+      <c r="AK133" t="n">
+        <v>0.35721</v>
+      </c>
+      <c r="AL133" t="n">
+        <v>0.44032</v>
+      </c>
+      <c r="AM133" t="n">
+        <v>0.18207</v>
+      </c>
+      <c r="AN133" t="n">
+        <v>-0.0054</v>
+      </c>
+      <c r="AO133" t="n">
+        <v>0.00029</v>
+      </c>
+      <c r="AP133" t="n">
+        <v>0.30384</v>
+      </c>
+      <c r="AQ133" t="n">
+        <v>0.30367</v>
+      </c>
+      <c r="AR133" t="n">
+        <v>0.31717</v>
+      </c>
+      <c r="AS133" t="n">
+        <v>0.35893</v>
+      </c>
+      <c r="AT133" t="n">
+        <v>0.34832</v>
+      </c>
+      <c r="AU133" t="n">
+        <v>0.36281</v>
+      </c>
+      <c r="AV133" t="n">
+        <v>0.26377</v>
+      </c>
+      <c r="AW133" t="n">
+        <v>0.21329</v>
+      </c>
+      <c r="AX133" t="n">
+        <v>0.27392</v>
+      </c>
+      <c r="AY133" t="n">
+        <v>0.09004999999999999</v>
+      </c>
+      <c r="AZ133" t="n">
+        <v>-0.04163</v>
+      </c>
+      <c r="BA133" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BB133" t="n">
+        <v>0.25948</v>
+      </c>
+      <c r="BC133" t="n">
+        <v>0.27055</v>
+      </c>
+      <c r="BD133" t="n">
+        <v>0.7122999999999999</v>
+      </c>
+      <c r="BE133" t="n">
+        <v>0.3878</v>
+      </c>
+      <c r="BF133" t="n">
+        <v>0.23959</v>
+      </c>
+      <c r="BG133" t="n">
+        <v>0.0988</v>
+      </c>
+      <c r="BH133" t="n">
+        <v>0.04644</v>
+      </c>
+      <c r="BI133" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BJ133" t="n">
+        <v>0.21663</v>
+      </c>
+      <c r="BK133" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BL133" t="n">
+        <v>0.3255</v>
+      </c>
+      <c r="BM133" t="n">
+        <v>0.31863</v>
+      </c>
+      <c r="BN133" t="n">
+        <v>0.30117</v>
+      </c>
+      <c r="BO133" t="n">
+        <v>0.3137200000000001</v>
+      </c>
+      <c r="BP133" t="n">
+        <v>0.33344</v>
+      </c>
+      <c r="BQ133" t="n">
+        <v>0.30978</v>
+      </c>
+      <c r="BR133" t="n">
+        <v>0.31262</v>
+      </c>
+      <c r="BS133" t="n">
+        <v>0.30488</v>
+      </c>
+      <c r="BT133" t="n">
+        <v>0.31913</v>
+      </c>
+      <c r="BU133" t="n">
+        <v>0.29648</v>
+      </c>
+      <c r="BV133" t="n">
+        <v>0.30065</v>
+      </c>
+      <c r="BW133" t="n">
+        <v>0.30954</v>
+      </c>
+      <c r="BX133" t="n">
+        <v>0.37736</v>
+      </c>
+      <c r="BY133" t="n">
+        <v>0.48179</v>
+      </c>
+      <c r="BZ133" t="n">
+        <v>0.42436</v>
+      </c>
+      <c r="CA133" t="n">
+        <v>0.50589</v>
+      </c>
+      <c r="CB133" t="n">
+        <v>0.50717</v>
+      </c>
+      <c r="CC133" t="n">
+        <v>0.36444</v>
+      </c>
+      <c r="CD133" t="n">
+        <v>0.52271</v>
+      </c>
+      <c r="CE133" t="n">
+        <v>0.61578</v>
+      </c>
+      <c r="CF133" t="n">
+        <v>0.40963</v>
+      </c>
+      <c r="CG133" t="n">
+        <v>0.54031</v>
+      </c>
+      <c r="CH133" t="n">
+        <v>0.7170299999999999</v>
+      </c>
+      <c r="CI133" t="n">
+        <v>0.46848</v>
+      </c>
+      <c r="CJ133" t="n">
+        <v>0.53195</v>
+      </c>
+      <c r="CK133" t="n">
+        <v>0.80991</v>
+      </c>
+      <c r="CL133" t="n">
+        <v>0.7454299999999999</v>
+      </c>
+      <c r="CM133" t="n">
+        <v>0.59661</v>
+      </c>
+      <c r="CN133" t="n">
+        <v>0.64501</v>
+      </c>
+      <c r="CO133" t="n">
+        <v>0.3574</v>
+      </c>
+      <c r="CP133" t="n">
+        <v>0.3926</v>
+      </c>
+      <c r="CQ133" t="n">
+        <v>0.48066</v>
+      </c>
+      <c r="CR133" t="n">
+        <v>0.47944</v>
+      </c>
+      <c r="CS133" t="n">
+        <v>0.47279</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="2" t="n">
+        <v>46157</v>
+      </c>
+      <c r="B134" t="n">
+        <v>0.41944</v>
+      </c>
+      <c r="C134" t="n">
+        <v>0.50378</v>
+      </c>
+      <c r="D134" t="n">
+        <v>0.41351</v>
+      </c>
+      <c r="E134" t="n">
+        <v>0.44511</v>
+      </c>
+      <c r="F134" t="n">
+        <v>0.4584</v>
+      </c>
+      <c r="G134" t="n">
+        <v>0.43692</v>
+      </c>
+      <c r="H134" t="n">
+        <v>0.42654</v>
+      </c>
+      <c r="I134" t="n">
+        <v>0.44839</v>
+      </c>
+      <c r="J134" t="n">
+        <v>0.41787</v>
+      </c>
+      <c r="K134" t="n">
+        <v>0.40085</v>
+      </c>
+      <c r="L134" t="n">
+        <v>0.4577</v>
+      </c>
+      <c r="M134" t="n">
+        <v>0.39938</v>
+      </c>
+      <c r="N134" t="n">
+        <v>0.4071</v>
+      </c>
+      <c r="O134" t="n">
+        <v>0.39874</v>
+      </c>
+      <c r="P134" t="n">
+        <v>0.38864</v>
+      </c>
+      <c r="Q134" t="n">
+        <v>0.38003</v>
+      </c>
+      <c r="R134" t="n">
+        <v>0.37498</v>
+      </c>
+      <c r="S134" t="n">
+        <v>0.36009</v>
+      </c>
+      <c r="T134" t="n">
+        <v>0.35689</v>
+      </c>
+      <c r="U134" t="n">
+        <v>0.36587</v>
+      </c>
+      <c r="V134" t="n">
+        <v>0.37693</v>
+      </c>
+      <c r="W134" t="n">
+        <v>0.37129</v>
+      </c>
+      <c r="X134" t="n">
+        <v>0.36023</v>
+      </c>
+      <c r="Y134" t="n">
+        <v>0.35987</v>
+      </c>
+      <c r="Z134" t="n">
+        <v>0.36587</v>
+      </c>
+      <c r="AA134" t="n">
+        <v>0.38665</v>
+      </c>
+      <c r="AB134" t="n">
+        <v>0.39026</v>
+      </c>
+      <c r="AC134" t="n">
+        <v>0.37964</v>
+      </c>
+      <c r="AD134" t="n">
+        <v>0.36653</v>
+      </c>
+      <c r="AE134" t="n">
+        <v>0.36141</v>
+      </c>
+      <c r="AF134" t="n">
+        <v>0.35514</v>
+      </c>
+      <c r="AG134" t="n">
+        <v>0.37967</v>
+      </c>
+      <c r="AH134" t="n">
+        <v>0.39935</v>
+      </c>
+      <c r="AI134" t="n">
+        <v>0.36052</v>
+      </c>
+      <c r="AJ134" t="n">
+        <v>0.38767</v>
+      </c>
+      <c r="AK134" t="n">
+        <v>0.38366</v>
+      </c>
+      <c r="AL134" t="n">
+        <v>0.3937</v>
+      </c>
+      <c r="AM134" t="n">
+        <v>0.38663</v>
+      </c>
+      <c r="AN134" t="n">
+        <v>0.35165</v>
+      </c>
+      <c r="AO134" t="n">
+        <v>0.3683</v>
+      </c>
+      <c r="AP134" t="n">
+        <v>0.3427</v>
+      </c>
+      <c r="AQ134" t="n">
+        <v>0.32767</v>
+      </c>
+      <c r="AR134" t="n">
+        <v>0.23049</v>
+      </c>
+      <c r="AS134" t="n">
+        <v>0.24675</v>
+      </c>
+      <c r="AT134" t="n">
+        <v>0.16136</v>
+      </c>
+      <c r="AU134" t="n">
+        <v>0.30257</v>
+      </c>
+      <c r="AV134" t="n">
+        <v>0.21119</v>
+      </c>
+      <c r="AW134" t="n">
+        <v>0.41416</v>
+      </c>
+      <c r="AX134" t="n">
+        <v>0.0557</v>
+      </c>
+      <c r="AY134" t="n">
+        <v>0.24965</v>
+      </c>
+      <c r="AZ134" t="n">
+        <v>0.39793</v>
+      </c>
+      <c r="BA134" t="n">
+        <v>0.41832</v>
+      </c>
+      <c r="BB134" t="n">
+        <v>0.46725</v>
+      </c>
+      <c r="BC134" t="n">
+        <v>0.4648</v>
+      </c>
+      <c r="BD134" t="n">
+        <v>0.494</v>
+      </c>
+      <c r="BE134" t="n">
+        <v>0.47551</v>
+      </c>
+      <c r="BF134" t="n">
+        <v>0.31642</v>
+      </c>
+      <c r="BG134" t="n">
+        <v>0.31037</v>
+      </c>
+      <c r="BH134" t="n">
+        <v>0.008279999999999999</v>
+      </c>
+      <c r="BI134" t="n">
+        <v>0.18956</v>
+      </c>
+      <c r="BJ134" t="n">
+        <v>0.30261</v>
+      </c>
+      <c r="BK134" t="n">
+        <v>0.29283</v>
+      </c>
+      <c r="BL134" t="n">
+        <v>0.31816</v>
+      </c>
+      <c r="BM134" t="n">
+        <v>0.35266</v>
+      </c>
+      <c r="BN134" t="n">
+        <v>0.35011</v>
+      </c>
+      <c r="BO134" t="n">
+        <v>0.3483</v>
+      </c>
+      <c r="BP134" t="n">
+        <v>0.34883</v>
+      </c>
+      <c r="BQ134" t="n">
+        <v>0.35722</v>
+      </c>
+      <c r="BR134" t="n">
+        <v>0.35895</v>
+      </c>
+      <c r="BS134" t="n">
+        <v>0.34588</v>
+      </c>
+      <c r="BT134" t="n">
+        <v>0.40946</v>
+      </c>
+      <c r="BU134" t="n">
+        <v>0.40917</v>
+      </c>
+      <c r="BV134" t="n">
+        <v>0.36329</v>
+      </c>
+      <c r="BW134" t="n">
+        <v>0.4118</v>
+      </c>
+      <c r="BX134" t="n">
+        <v>0.3975</v>
+      </c>
+      <c r="BY134" t="n">
+        <v>0.38195</v>
+      </c>
+      <c r="BZ134" t="n">
+        <v>0.3585</v>
+      </c>
+      <c r="CA134" t="n">
+        <v>0.33438</v>
+      </c>
+      <c r="CB134" t="n">
+        <v>0.37812</v>
+      </c>
+      <c r="CC134" t="n">
+        <v>0.38548</v>
+      </c>
+      <c r="CD134" t="n">
+        <v>0.40585</v>
+      </c>
+      <c r="CE134" t="n">
+        <v>0.4011</v>
+      </c>
+      <c r="CF134" t="n">
+        <v>0.34399</v>
+      </c>
+      <c r="CG134" t="n">
+        <v>0.36511</v>
+      </c>
+      <c r="CH134" t="n">
+        <v>0.37807</v>
+      </c>
+      <c r="CI134" t="n">
+        <v>0.39946</v>
+      </c>
+      <c r="CJ134" t="n">
+        <v>0.36009</v>
+      </c>
+      <c r="CK134" t="n">
+        <v>0.37952</v>
+      </c>
+      <c r="CL134" t="n">
+        <v>0.35509</v>
+      </c>
+      <c r="CM134" t="n">
+        <v>0.39963</v>
+      </c>
+      <c r="CN134" t="n">
+        <v>0.38059</v>
+      </c>
+      <c r="CO134" t="n">
+        <v>0.37502</v>
+      </c>
+      <c r="CP134" t="n">
+        <v>0.36036</v>
+      </c>
+      <c r="CQ134" t="n">
+        <v>0.39379</v>
+      </c>
+      <c r="CR134" t="n">
+        <v>0.37899</v>
+      </c>
+      <c r="CS134" t="n">
+        <v>0.36408</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="2" t="n">
+        <v>46158</v>
+      </c>
+      <c r="B135" t="n">
+        <v>0.33128</v>
+      </c>
+      <c r="C135" t="n">
+        <v>0.44266</v>
+      </c>
+      <c r="D135" t="n">
+        <v>0.35452</v>
+      </c>
+      <c r="E135" t="n">
+        <v>0.31724</v>
+      </c>
+      <c r="F135" t="n">
+        <v>0.31802</v>
+      </c>
+      <c r="G135" t="n">
+        <v>0.33228</v>
+      </c>
+      <c r="H135" t="n">
+        <v>0.37692</v>
+      </c>
+      <c r="I135" t="n">
+        <v>0.35081</v>
+      </c>
+      <c r="J135" t="n">
+        <v>0.37677</v>
+      </c>
+      <c r="K135" t="n">
+        <v>0.36493</v>
+      </c>
+      <c r="L135" t="n">
+        <v>0.35581</v>
+      </c>
+      <c r="M135" t="n">
+        <v>0.35365</v>
+      </c>
+      <c r="N135" t="n">
+        <v>0.35147</v>
+      </c>
+      <c r="O135" t="n">
+        <v>0.35715</v>
+      </c>
+      <c r="P135" t="n">
+        <v>0.34765</v>
+      </c>
+      <c r="Q135" t="n">
+        <v>0.35044</v>
+      </c>
+      <c r="R135" t="n">
+        <v>0.34846</v>
+      </c>
+      <c r="S135" t="n">
+        <v>0.33927</v>
+      </c>
+      <c r="T135" t="n">
+        <v>0.33154</v>
+      </c>
+      <c r="U135" t="n">
+        <v>0.33972</v>
+      </c>
+      <c r="V135" t="n">
+        <v>0.34043</v>
+      </c>
+      <c r="W135" t="n">
+        <v>0.33553</v>
+      </c>
+      <c r="X135" t="n">
+        <v>0.34054</v>
+      </c>
+      <c r="Y135" t="n">
+        <v>0.34554</v>
+      </c>
+      <c r="Z135" t="n">
+        <v>0.33101</v>
+      </c>
+      <c r="AA135" t="n">
+        <v>0.33055</v>
+      </c>
+      <c r="AB135" t="n">
+        <v>0.338</v>
+      </c>
+      <c r="AC135" t="n">
+        <v>0.33808</v>
+      </c>
+      <c r="AD135" t="n">
+        <v>0.3444</v>
+      </c>
+      <c r="AE135" t="n">
+        <v>0.32574</v>
+      </c>
+      <c r="AF135" t="n">
+        <v>0.3166600000000001</v>
+      </c>
+      <c r="AG135" t="n">
+        <v>0.31108</v>
+      </c>
+      <c r="AH135" t="n">
+        <v>0.32453</v>
+      </c>
+      <c r="AI135" t="n">
+        <v>0.12594</v>
+      </c>
+      <c r="AJ135" t="n">
+        <v>0.32676</v>
+      </c>
+      <c r="AK135" t="n">
+        <v>0.32143</v>
+      </c>
+      <c r="AL135" t="n">
+        <v>0.31573</v>
+      </c>
+      <c r="AM135" t="n">
+        <v>0.23154</v>
+      </c>
+      <c r="AN135" t="n">
+        <v>0.29341</v>
+      </c>
+      <c r="AO135" t="n">
+        <v>0.23315</v>
+      </c>
+      <c r="AP135" t="n">
+        <v>0.22689</v>
+      </c>
+      <c r="AQ135" t="n">
+        <v>0.24613</v>
+      </c>
+      <c r="AR135" t="n">
+        <v>-0.02466</v>
+      </c>
+      <c r="AS135" t="n">
+        <v>0.12981</v>
+      </c>
+      <c r="AT135" t="n">
+        <v>0.22451</v>
+      </c>
+      <c r="AU135" t="n">
+        <v>0.28509</v>
+      </c>
+      <c r="AV135" t="n">
+        <v>-0.02398</v>
+      </c>
+      <c r="AW135" t="n">
+        <v>0.1489</v>
+      </c>
+      <c r="AX135" t="n">
+        <v>0.04338</v>
+      </c>
+      <c r="AY135" t="n">
+        <v>0.25517</v>
+      </c>
+      <c r="AZ135" t="n">
+        <v>-0.03679</v>
+      </c>
+      <c r="BA135" t="n">
+        <v>0.14237</v>
+      </c>
+      <c r="BB135" t="n">
+        <v>0.1514</v>
+      </c>
+      <c r="BC135" t="n">
+        <v>0.004690000000000001</v>
+      </c>
+      <c r="BD135" t="n">
+        <v>0.30319</v>
+      </c>
+      <c r="BE135" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BF135" t="n">
+        <v>0.2158</v>
+      </c>
+      <c r="BG135" t="n">
+        <v>0.2266</v>
+      </c>
+      <c r="BH135" t="n">
+        <v>0.13888</v>
+      </c>
+      <c r="BI135" t="n">
+        <v>0.21071</v>
+      </c>
+      <c r="BJ135" t="n">
+        <v>0.26499</v>
+      </c>
+      <c r="BK135" t="n">
+        <v>0.28307</v>
+      </c>
+      <c r="BL135" t="n">
+        <v>0.25812</v>
+      </c>
+      <c r="BM135" t="n">
+        <v>0.2965</v>
+      </c>
+      <c r="BN135" t="n">
+        <v>0.32585</v>
+      </c>
+      <c r="BO135" t="n">
+        <v>0.28529</v>
+      </c>
+      <c r="BP135" t="n">
+        <v>0.34919</v>
+      </c>
+      <c r="BQ135" t="n">
+        <v>0.34628</v>
+      </c>
+      <c r="BR135" t="n">
+        <v>0.34967</v>
+      </c>
+      <c r="BS135" t="n">
+        <v>0.33513</v>
+      </c>
+      <c r="BT135" t="n">
+        <v>0.33862</v>
+      </c>
+      <c r="BU135" t="n">
+        <v>0.32624</v>
+      </c>
+      <c r="BV135" t="n">
+        <v>0.33072</v>
+      </c>
+      <c r="BW135" t="n">
+        <v>0.31803</v>
+      </c>
+      <c r="BX135" t="n">
+        <v>0.3135</v>
+      </c>
+      <c r="BY135" t="n">
+        <v>0.34319</v>
+      </c>
+      <c r="BZ135" t="n">
+        <v>0.30643</v>
+      </c>
+      <c r="CA135" t="n">
+        <v>0.33766</v>
+      </c>
+      <c r="CB135" t="n">
+        <v>0.34512</v>
+      </c>
+      <c r="CC135" t="n">
+        <v>0.31857</v>
+      </c>
+      <c r="CD135" t="n">
+        <v>0.34307</v>
+      </c>
+      <c r="CE135" t="n">
+        <v>0.32298</v>
+      </c>
+      <c r="CF135" t="n">
+        <v>0.34458</v>
+      </c>
+      <c r="CG135" t="n">
+        <v>0.31869</v>
+      </c>
+      <c r="CH135" t="n">
+        <v>0.34442</v>
+      </c>
+      <c r="CI135" t="n">
+        <v>0.34184</v>
+      </c>
+      <c r="CJ135" t="n">
+        <v>0.34196</v>
+      </c>
+      <c r="CK135" t="n">
+        <v>0.34319</v>
+      </c>
+      <c r="CL135" t="n">
+        <v>0.36604</v>
+      </c>
+      <c r="CM135" t="n">
+        <v>0.37075</v>
+      </c>
+      <c r="CN135" t="n">
+        <v>0.36071</v>
+      </c>
+      <c r="CO135" t="n">
+        <v>0.3504</v>
+      </c>
+      <c r="CP135" t="n">
+        <v>0.35052</v>
+      </c>
+      <c r="CQ135" t="n">
+        <v>0.35013</v>
+      </c>
+      <c r="CR135" t="n">
+        <v>0.35044</v>
+      </c>
+      <c r="CS135" t="n">
+        <v>0.35194</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="2" t="n">
+        <v>46159</v>
+      </c>
+      <c r="B136" t="n">
+        <v>0.32314</v>
+      </c>
+      <c r="C136" t="n">
+        <v>0.32338</v>
+      </c>
+      <c r="D136" t="n">
+        <v>0.33882</v>
+      </c>
+      <c r="E136" t="n">
+        <v>0.34289</v>
+      </c>
+      <c r="F136" t="n">
+        <v>0.31933</v>
+      </c>
+      <c r="G136" t="n">
+        <v>0.3399</v>
+      </c>
+      <c r="H136" t="n">
+        <v>0.33201</v>
+      </c>
+      <c r="I136" t="n">
+        <v>0.32565</v>
+      </c>
+      <c r="J136" t="n">
+        <v>0.32056</v>
+      </c>
+      <c r="K136" t="n">
+        <v>0.32025</v>
+      </c>
+      <c r="L136" t="n">
+        <v>0.3108</v>
+      </c>
+      <c r="M136" t="n">
+        <v>0.3105</v>
+      </c>
+      <c r="N136" t="n">
+        <v>0.31533</v>
+      </c>
+      <c r="O136" t="n">
+        <v>0.31074</v>
+      </c>
+      <c r="P136" t="n">
+        <v>0.31127</v>
+      </c>
+      <c r="Q136" t="n">
+        <v>0.3112</v>
+      </c>
+      <c r="R136" t="n">
+        <v>0.31102</v>
+      </c>
+      <c r="S136" t="n">
+        <v>0.31717</v>
+      </c>
+      <c r="T136" t="n">
+        <v>0.30705</v>
+      </c>
+      <c r="U136" t="n">
+        <v>0.30705</v>
+      </c>
+      <c r="V136" t="n">
+        <v>0.30954</v>
+      </c>
+      <c r="W136" t="n">
+        <v>0.31031</v>
+      </c>
+      <c r="X136" t="n">
+        <v>0.30639</v>
+      </c>
+      <c r="Y136" t="n">
+        <v>0.30705</v>
+      </c>
+      <c r="Z136" t="n">
+        <v>0.30765</v>
+      </c>
+      <c r="AA136" t="n">
+        <v>0.31067</v>
+      </c>
+      <c r="AB136" t="n">
+        <v>0.31161</v>
+      </c>
+      <c r="AC136" t="n">
+        <v>0.29108</v>
+      </c>
+      <c r="AD136" t="n">
+        <v>0.22795</v>
+      </c>
+      <c r="AE136" t="n">
+        <v>0.21744</v>
+      </c>
+      <c r="AF136" t="n">
+        <v>0.15141</v>
+      </c>
+      <c r="AG136" t="n">
+        <v>0.18093</v>
+      </c>
+      <c r="AH136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AI136" t="n">
+        <v>0.01497</v>
+      </c>
+      <c r="AJ136" t="n">
+        <v>-0.00273</v>
+      </c>
+      <c r="AK136" t="n">
+        <v>-0.0433</v>
+      </c>
+      <c r="AL136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AM136" t="n">
+        <v>-0.04597</v>
+      </c>
+      <c r="AN136" t="n">
+        <v>-0.03357</v>
+      </c>
+      <c r="AO136" t="n">
+        <v>-0.04269</v>
+      </c>
+      <c r="AP136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AQ136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AR136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AS136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AT136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AU136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AV136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AW136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AX136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AZ136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BA136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BB136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BC136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BD136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BE136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BF136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BG136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BH136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BI136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BJ136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BK136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BL136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BM136" t="n">
+        <v>-0.04949</v>
+      </c>
+      <c r="BN136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BO136" t="n">
+        <v>0.17047</v>
+      </c>
+      <c r="BP136" t="n">
+        <v>0.21532</v>
+      </c>
+      <c r="BQ136" t="n">
+        <v>0.26705</v>
+      </c>
+      <c r="BR136" t="n">
+        <v>0.24301</v>
+      </c>
+      <c r="BS136" t="n">
+        <v>0.24536</v>
+      </c>
+      <c r="BT136" t="n">
+        <v>0.24512</v>
+      </c>
+      <c r="BU136" t="n">
+        <v>0.25066</v>
+      </c>
+      <c r="BV136" t="n">
+        <v>0.26413</v>
+      </c>
+      <c r="BW136" t="n">
+        <v>0.28728</v>
+      </c>
+      <c r="BX136" t="n">
+        <v>0.27277</v>
+      </c>
+      <c r="BY136" t="n">
+        <v>0.2693</v>
+      </c>
+      <c r="BZ136" t="n">
+        <v>0.25841</v>
+      </c>
+      <c r="CA136" t="n">
+        <v>0.30363</v>
+      </c>
+      <c r="CB136" t="n">
+        <v>0.27768</v>
+      </c>
+      <c r="CC136" t="n">
+        <v>0.28213</v>
+      </c>
+      <c r="CD136" t="n">
+        <v>0.26622</v>
+      </c>
+      <c r="CE136" t="n">
+        <v>0.28151</v>
+      </c>
+      <c r="CF136" t="n">
+        <v>0.26838</v>
+      </c>
+      <c r="CG136" t="n">
+        <v>0.28446</v>
+      </c>
+      <c r="CH136" t="n">
+        <v>0.27442</v>
+      </c>
+      <c r="CI136" t="n">
+        <v>0.29511</v>
+      </c>
+      <c r="CJ136" t="n">
+        <v>0.36407</v>
+      </c>
+      <c r="CK136" t="n">
+        <v>0.30185</v>
+      </c>
+      <c r="CL136" t="n">
+        <v>0.30614</v>
+      </c>
+      <c r="CM136" t="n">
+        <v>0.28612</v>
+      </c>
+      <c r="CN136" t="n">
+        <v>0.25715</v>
+      </c>
+      <c r="CO136" t="n">
+        <v>0.26736</v>
+      </c>
+      <c r="CP136" t="n">
+        <v>0.25275</v>
+      </c>
+      <c r="CQ136" t="n">
+        <v>0.23734</v>
+      </c>
+      <c r="CR136" t="n">
+        <v>0.19179</v>
+      </c>
+      <c r="CS136" t="n">
+        <v>0.05827</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="2" t="n">
+        <v>46160</v>
+      </c>
+      <c r="B137" t="n">
+        <v>0.2979</v>
+      </c>
+      <c r="C137" t="n">
+        <v>0.41729</v>
+      </c>
+      <c r="D137" t="n">
+        <v>0.03754</v>
+      </c>
+      <c r="E137" t="n">
+        <v>0.06783</v>
+      </c>
+      <c r="F137" t="n">
+        <v>0.25127</v>
+      </c>
+      <c r="G137" t="n">
+        <v>0.22806</v>
+      </c>
+      <c r="H137" t="n">
+        <v>0.22569</v>
+      </c>
+      <c r="I137" t="n">
+        <v>0.14997</v>
+      </c>
+      <c r="J137" t="n">
+        <v>0.27017</v>
+      </c>
+      <c r="K137" t="n">
+        <v>0.26391</v>
+      </c>
+      <c r="L137" t="n">
+        <v>0.24645</v>
+      </c>
+      <c r="M137" t="n">
+        <v>0.22372</v>
+      </c>
+      <c r="N137" t="n">
+        <v>0.20728</v>
+      </c>
+      <c r="O137" t="n">
+        <v>0.19075</v>
+      </c>
+      <c r="P137" t="n">
+        <v>0.21555</v>
+      </c>
+      <c r="Q137" t="n">
+        <v>0.22622</v>
+      </c>
+      <c r="R137" t="n">
+        <v>0.171</v>
+      </c>
+      <c r="S137" t="n">
+        <v>0.19104</v>
+      </c>
+      <c r="T137" t="n">
+        <v>0.22311</v>
+      </c>
+      <c r="U137" t="n">
+        <v>0.2231</v>
+      </c>
+      <c r="V137" t="n">
+        <v>0.2443</v>
+      </c>
+      <c r="W137" t="n">
+        <v>0.2327</v>
+      </c>
+      <c r="X137" t="n">
+        <v>0.21582</v>
+      </c>
+      <c r="Y137" t="n">
+        <v>0.26405</v>
+      </c>
+      <c r="Z137" t="n">
+        <v>0.22753</v>
+      </c>
+      <c r="AA137" t="n">
+        <v>0.27041</v>
+      </c>
+      <c r="AB137" t="n">
+        <v>0.32665</v>
+      </c>
+      <c r="AC137" t="n">
+        <v>0.27177</v>
+      </c>
+      <c r="AD137" t="n">
+        <v>0.2474</v>
+      </c>
+      <c r="AE137" t="n">
+        <v>0.24865</v>
+      </c>
+      <c r="AF137" t="n">
+        <v>0.18488</v>
+      </c>
+      <c r="AG137" t="n">
+        <v>0.06742000000000001</v>
+      </c>
+      <c r="AH137" t="n">
+        <v>0.49895</v>
+      </c>
+      <c r="AI137" t="n">
+        <v>0.50299</v>
+      </c>
+      <c r="AJ137" t="n">
+        <v>0.51113</v>
+      </c>
+      <c r="AK137" t="n">
+        <v>0.35094</v>
+      </c>
+      <c r="AL137" t="n">
+        <v>0.0312</v>
+      </c>
+      <c r="AM137" t="n">
+        <v>0.18968</v>
+      </c>
+      <c r="AN137" t="n">
+        <v>-0.04865</v>
+      </c>
+      <c r="AO137" t="n">
+        <v>0.19772</v>
+      </c>
+      <c r="AP137" t="n">
+        <v>0.09915</v>
+      </c>
+      <c r="AQ137" t="n">
+        <v>0.04482999999999999</v>
+      </c>
+      <c r="AR137" t="n">
+        <v>0.05039</v>
+      </c>
+      <c r="AS137" t="n">
+        <v>-0.004719999999999999</v>
+      </c>
+      <c r="AT137" t="n">
+        <v>0.2081</v>
+      </c>
+      <c r="AU137" t="n">
+        <v>0.03293</v>
+      </c>
+      <c r="AV137" t="n">
+        <v>0.2915</v>
+      </c>
+      <c r="AW137" t="n">
+        <v>-0.04665</v>
+      </c>
+      <c r="AX137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY137" t="n">
+        <v>-0.04584000000000001</v>
+      </c>
+      <c r="AZ137" t="n">
+        <v>0.02837</v>
+      </c>
+      <c r="BA137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BB137" t="n">
+        <v>0.13219</v>
+      </c>
+      <c r="BC137" t="n">
+        <v>-0.03913000000000001</v>
+      </c>
+      <c r="BD137" t="n">
+        <v>0.04368</v>
+      </c>
+      <c r="BE137" t="n">
+        <v>0.00331</v>
+      </c>
+      <c r="BF137" t="n">
+        <v>0.07648000000000001</v>
+      </c>
+      <c r="BG137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BH137" t="n">
+        <v>0.02779</v>
+      </c>
+      <c r="BI137" t="n">
+        <v>-0.01611</v>
+      </c>
+      <c r="BJ137" t="n">
+        <v>0.02553</v>
+      </c>
+      <c r="BK137" t="n">
+        <v>0.05358</v>
+      </c>
+      <c r="BL137" t="n">
+        <v>0.19695</v>
+      </c>
+      <c r="BM137" t="n">
+        <v>0.25735</v>
+      </c>
+      <c r="BN137" t="n">
+        <v>0.21258</v>
+      </c>
+      <c r="BO137" t="n">
+        <v>0.23539</v>
+      </c>
+      <c r="BP137" t="n">
+        <v>0.26335</v>
+      </c>
+      <c r="BQ137" t="n">
+        <v>0.26776</v>
+      </c>
+      <c r="BR137" t="n">
+        <v>0.26471</v>
+      </c>
+      <c r="BS137" t="n">
+        <v>0.2921</v>
+      </c>
+      <c r="BT137" t="n">
+        <v>0.30516</v>
+      </c>
+      <c r="BU137" t="n">
+        <v>0.26928</v>
+      </c>
+      <c r="BV137" t="n">
+        <v>0.29275</v>
+      </c>
+      <c r="BW137" t="n">
+        <v>0.28583</v>
+      </c>
+      <c r="BX137" t="n">
+        <v>0.26667</v>
+      </c>
+      <c r="BY137" t="n">
+        <v>0.2957</v>
+      </c>
+      <c r="BZ137" t="n">
+        <v>0.27219</v>
+      </c>
+      <c r="CA137" t="n">
+        <v>0.30727</v>
+      </c>
+      <c r="CB137" t="n">
+        <v>0.30723</v>
+      </c>
+      <c r="CC137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CD137" t="n">
+        <v>0.29622</v>
+      </c>
+      <c r="CE137" t="n">
+        <v>0.29942</v>
+      </c>
+      <c r="CF137" t="n">
+        <v>0.29937</v>
+      </c>
+      <c r="CG137" t="n">
+        <v>0.34338</v>
+      </c>
+      <c r="CH137" t="n">
+        <v>0.32372</v>
+      </c>
+      <c r="CI137" t="n">
+        <v>0.3628</v>
+      </c>
+      <c r="CJ137" t="n">
+        <v>0.28642</v>
+      </c>
+      <c r="CK137" t="n">
+        <v>0.30522</v>
+      </c>
+      <c r="CL137" t="n">
+        <v>0.31216</v>
+      </c>
+      <c r="CM137" t="n">
+        <v>0.29812</v>
+      </c>
+      <c r="CN137" t="n">
+        <v>0.32657</v>
+      </c>
+      <c r="CO137" t="n">
+        <v>0.32934</v>
+      </c>
+      <c r="CP137" t="n">
+        <v>0.33057</v>
+      </c>
+      <c r="CQ137" t="n">
+        <v>0.32683</v>
+      </c>
+      <c r="CR137" t="n">
+        <v>0.33958</v>
+      </c>
+      <c r="CS137" t="n">
+        <v>0.32498</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="2" t="n">
+        <v>46161</v>
+      </c>
+      <c r="B138" t="n">
+        <v>0.33021</v>
+      </c>
+      <c r="C138" t="n">
+        <v>0.3545</v>
+      </c>
+      <c r="D138" t="n">
+        <v>0.36615</v>
+      </c>
+      <c r="E138" t="n">
+        <v>0.33828</v>
+      </c>
+      <c r="F138" t="n">
+        <v>0.33587</v>
+      </c>
+      <c r="G138" t="n">
+        <v>0.33533</v>
+      </c>
+      <c r="H138" t="n">
+        <v>0.33013</v>
+      </c>
+      <c r="I138" t="n">
+        <v>0.33048</v>
+      </c>
+      <c r="J138" t="n">
+        <v>0.33069</v>
+      </c>
+      <c r="K138" t="n">
+        <v>0.33365</v>
+      </c>
+      <c r="L138" t="n">
+        <v>0.32881</v>
+      </c>
+      <c r="M138" t="n">
+        <v>0.34144</v>
+      </c>
+      <c r="N138" t="n">
+        <v>0.33541</v>
+      </c>
+      <c r="O138" t="n">
+        <v>0.33433</v>
+      </c>
+      <c r="P138" t="n">
+        <v>0.32755</v>
+      </c>
+      <c r="Q138" t="n">
+        <v>0.34426</v>
+      </c>
+      <c r="R138" t="n">
+        <v>0.08717</v>
+      </c>
+      <c r="S138" t="n">
+        <v>0.32617</v>
+      </c>
+      <c r="T138" t="n">
+        <v>0.32625</v>
+      </c>
+      <c r="U138" t="n">
+        <v>0.31962</v>
+      </c>
+      <c r="V138" t="n">
+        <v>0.33073</v>
+      </c>
+      <c r="W138" t="n">
+        <v>0.32749</v>
+      </c>
+      <c r="X138" t="n">
+        <v>0.32819</v>
+      </c>
+      <c r="Y138" t="n">
+        <v>0.33001</v>
+      </c>
+      <c r="Z138" t="n">
+        <v>0.33392</v>
+      </c>
+      <c r="AA138" t="n">
+        <v>0.34171</v>
+      </c>
+      <c r="AB138" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AC138" t="n">
+        <v>-0.02771</v>
+      </c>
+      <c r="AD138" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AE138" t="n">
+        <v>-0.03313</v>
+      </c>
+      <c r="AF138" t="n">
+        <v>-0.02152</v>
+      </c>
+      <c r="AG138" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AH138" t="n">
+        <v>-0.03655</v>
+      </c>
+      <c r="AI138" t="n">
+        <v>0.30159</v>
+      </c>
+      <c r="AJ138" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AK138" t="n">
+        <v>0.24956</v>
+      </c>
+      <c r="AL138" t="n">
+        <v>0.35962</v>
+      </c>
+      <c r="AM138" t="n">
+        <v>0.27315</v>
+      </c>
+      <c r="AN138" t="n">
+        <v>0.36152</v>
+      </c>
+      <c r="AO138" t="n">
+        <v>0.29669</v>
+      </c>
+      <c r="AP138" t="n">
+        <v>0.29184</v>
+      </c>
+      <c r="AQ138" t="n">
+        <v>0.28344</v>
+      </c>
+      <c r="AR138" t="n">
+        <v>0.30275</v>
+      </c>
+      <c r="AS138" t="n">
+        <v>0.26494</v>
+      </c>
+      <c r="AT138" t="n">
+        <v>0.3098399999999999</v>
+      </c>
+      <c r="AU138" t="n">
+        <v>0.30706</v>
+      </c>
+      <c r="AV138" t="n">
+        <v>0.28531</v>
+      </c>
+      <c r="AW138" t="n">
+        <v>0.28727</v>
+      </c>
+      <c r="AX138" t="n">
+        <v>0.10137</v>
+      </c>
+      <c r="AY138" t="n">
+        <v>0.2191</v>
+      </c>
+      <c r="AZ138" t="n">
+        <v>0.26951</v>
+      </c>
+      <c r="BA138" t="n">
+        <v>0.30332</v>
+      </c>
+      <c r="BB138" t="n">
+        <v>0.31137</v>
+      </c>
+      <c r="BC138" t="n">
+        <v>0.14958</v>
+      </c>
+      <c r="BD138" t="n">
+        <v>0.31793</v>
+      </c>
+      <c r="BE138" t="n">
+        <v>0.31529</v>
+      </c>
+      <c r="BF138" t="n">
+        <v>0.14014</v>
+      </c>
+      <c r="BG138" t="n">
+        <v>0.04797</v>
+      </c>
+      <c r="BH138" t="n">
+        <v>0.30849</v>
+      </c>
+      <c r="BI138" t="n">
+        <v>0.28963</v>
+      </c>
+      <c r="BJ138" t="n">
+        <v>0.30997</v>
+      </c>
+      <c r="BK138" t="n">
+        <v>0.31618</v>
+      </c>
+      <c r="BL138" t="n">
+        <v>0.31899</v>
+      </c>
+      <c r="BM138" t="n">
+        <v>0.3261</v>
+      </c>
+      <c r="BN138" t="n">
+        <v>0.33587</v>
+      </c>
+      <c r="BO138" t="n">
+        <v>0.32327</v>
+      </c>
+      <c r="BP138" t="n">
+        <v>0.3466</v>
+      </c>
+      <c r="BQ138" t="n">
+        <v>0.3275</v>
+      </c>
+      <c r="BR138" t="n">
+        <v>0.31638</v>
+      </c>
+      <c r="BS138" t="n">
+        <v>0.31429</v>
+      </c>
+      <c r="BT138" t="n">
+        <v>0.31605</v>
+      </c>
+      <c r="BU138" t="n">
+        <v>0.31542</v>
+      </c>
+      <c r="BV138" t="n">
+        <v>0.31556</v>
+      </c>
+      <c r="BW138" t="n">
+        <v>0.31635</v>
+      </c>
+      <c r="BX138" t="n">
+        <v>0.31193</v>
+      </c>
+      <c r="BY138" t="n">
+        <v>0.3117200000000001</v>
+      </c>
+      <c r="BZ138" t="n">
+        <v>0.31449</v>
+      </c>
+      <c r="CA138" t="n">
+        <v>0.31266</v>
+      </c>
+      <c r="CB138" t="n">
+        <v>0.31518</v>
+      </c>
+      <c r="CC138" t="n">
+        <v>0.37118</v>
+      </c>
+      <c r="CD138" t="n">
+        <v>0.31361</v>
+      </c>
+      <c r="CE138" t="n">
+        <v>-0.03265</v>
+      </c>
+      <c r="CF138" t="n">
+        <v>0.31029</v>
+      </c>
+      <c r="CG138" t="n">
+        <v>0.31414</v>
+      </c>
+      <c r="CH138" t="n">
+        <v>0.30705</v>
+      </c>
+      <c r="CI138" t="n">
+        <v>0.30509</v>
+      </c>
+      <c r="CJ138" t="n">
+        <v>0.31107</v>
+      </c>
+      <c r="CK138" t="n">
+        <v>0.31624</v>
+      </c>
+      <c r="CL138" t="n">
+        <v>0.31531</v>
+      </c>
+      <c r="CM138" t="n">
+        <v>0.36798</v>
+      </c>
+      <c r="CN138" t="n">
+        <v>0.35135</v>
+      </c>
+      <c r="CO138" t="n">
+        <v>0.31385</v>
+      </c>
+      <c r="CP138" t="n">
+        <v>0.33156</v>
+      </c>
+      <c r="CQ138" t="n">
+        <v>0.32528</v>
+      </c>
+      <c r="CR138" t="n">
+        <v>0.33056</v>
+      </c>
+      <c r="CS138" t="n">
+        <v>0.33078</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="2" t="n">
+        <v>46162</v>
+      </c>
+      <c r="B139" t="n">
+        <v>0.3271</v>
+      </c>
+      <c r="C139" t="n">
+        <v>0.37031</v>
+      </c>
+      <c r="D139" t="n">
+        <v>0.33089</v>
+      </c>
+      <c r="E139" t="n">
+        <v>0.33076</v>
+      </c>
+      <c r="F139" t="n">
+        <v>0.26367</v>
+      </c>
+      <c r="G139" t="n">
+        <v>0.31659</v>
+      </c>
+      <c r="H139" t="n">
+        <v>0.32011</v>
+      </c>
+      <c r="I139" t="n">
+        <v>0.32867</v>
+      </c>
+      <c r="J139" t="n">
+        <v>0.32915</v>
+      </c>
+      <c r="K139" t="n">
+        <v>0.33051</v>
+      </c>
+      <c r="L139" t="n">
+        <v>0.33161</v>
+      </c>
+      <c r="M139" t="n">
+        <v>0.33596</v>
+      </c>
+      <c r="N139" t="n">
+        <v>0.3451</v>
+      </c>
+      <c r="O139" t="n">
+        <v>0.28876</v>
+      </c>
+      <c r="P139" t="n">
+        <v>0.3492</v>
+      </c>
+      <c r="Q139" t="n">
+        <v>0.34067</v>
+      </c>
+      <c r="R139" t="n">
+        <v>0.33596</v>
+      </c>
+      <c r="S139" t="n">
+        <v>0.32055</v>
+      </c>
+      <c r="T139" t="n">
+        <v>0.32036</v>
+      </c>
+      <c r="U139" t="n">
+        <v>0.33047</v>
+      </c>
+      <c r="V139" t="n">
+        <v>0.34654</v>
+      </c>
+      <c r="W139" t="n">
+        <v>0.3311</v>
+      </c>
+      <c r="X139" t="n">
+        <v>0.34022</v>
+      </c>
+      <c r="Y139" t="n">
+        <v>0.35397</v>
+      </c>
+      <c r="Z139" t="n">
+        <v>0.3232</v>
+      </c>
+      <c r="AA139" t="n">
+        <v>0.36923</v>
+      </c>
+      <c r="AB139" t="n">
+        <v>0.35529</v>
+      </c>
+      <c r="AC139" t="n">
+        <v>0.36962</v>
+      </c>
+      <c r="AD139" t="n">
+        <v>0.35945</v>
+      </c>
+      <c r="AE139" t="n">
+        <v>0.31696</v>
+      </c>
+      <c r="AF139" t="n">
+        <v>-0.02094</v>
+      </c>
+      <c r="AG139" t="n">
+        <v>0.32977</v>
+      </c>
+      <c r="AH139" t="n">
+        <v>0.32233</v>
+      </c>
+      <c r="AI139" t="n">
+        <v>0.30125</v>
+      </c>
+      <c r="AJ139" t="n">
+        <v>0.43857</v>
+      </c>
+      <c r="AK139" t="n">
+        <v>0.29938</v>
+      </c>
+      <c r="AL139" t="n">
+        <v>0.5262100000000001</v>
+      </c>
+      <c r="AM139" t="n">
+        <v>0.06567000000000001</v>
+      </c>
+      <c r="AN139" t="n">
+        <v>0.26045</v>
+      </c>
+      <c r="AO139" t="n">
+        <v>0.26992</v>
+      </c>
+      <c r="AP139" t="n">
+        <v>0.31277</v>
+      </c>
+      <c r="AQ139" t="n">
+        <v>0.24699</v>
+      </c>
+      <c r="AR139" t="n">
+        <v>0.21565</v>
+      </c>
+      <c r="AS139" t="n">
+        <v>0.2424</v>
+      </c>
+      <c r="AT139" t="n">
+        <v>0.22962</v>
+      </c>
+      <c r="AU139" t="n">
+        <v>0.21055</v>
+      </c>
+      <c r="AV139" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AW139" t="n">
+        <v>0.21215</v>
+      </c>
+      <c r="AX139" t="n">
+        <v>0.30494</v>
+      </c>
+      <c r="AY139" t="n">
+        <v>0.36126</v>
+      </c>
+      <c r="AZ139" t="n">
+        <v>0.27199</v>
+      </c>
+      <c r="BA139" t="n">
+        <v>0.21131</v>
+      </c>
+      <c r="BB139" t="n">
+        <v>0.24088</v>
+      </c>
+      <c r="BC139" t="n">
+        <v>0.24829</v>
+      </c>
+      <c r="BD139" t="n">
+        <v>0.34325</v>
+      </c>
+      <c r="BE139" t="n">
+        <v>0.36322</v>
+      </c>
+      <c r="BF139" t="n">
+        <v>0.32516</v>
+      </c>
+      <c r="BG139" t="n">
+        <v>0.17991</v>
+      </c>
+      <c r="BH139" t="n">
+        <v>0.23438</v>
+      </c>
+      <c r="BI139" t="n">
+        <v>0.27816</v>
+      </c>
+      <c r="BJ139" t="n">
+        <v>0.26196</v>
+      </c>
+      <c r="BK139" t="n">
+        <v>0.2597</v>
+      </c>
+      <c r="BL139" t="n">
+        <v>0.23561</v>
+      </c>
+      <c r="BM139" t="n">
+        <v>0.25776</v>
+      </c>
+      <c r="BN139" t="n">
+        <v>0.30946</v>
+      </c>
+      <c r="BO139" t="n">
+        <v>0.37818</v>
+      </c>
+      <c r="BP139" t="n">
+        <v>0.36021</v>
+      </c>
+      <c r="BQ139" t="n">
+        <v>0.4281</v>
+      </c>
+      <c r="BR139" t="n">
+        <v>0.44045</v>
+      </c>
+      <c r="BS139" t="n">
+        <v>0.41988</v>
+      </c>
+      <c r="BT139" t="n">
+        <v>0.43957</v>
+      </c>
+      <c r="BU139" t="n">
+        <v>0.34624</v>
+      </c>
+      <c r="BV139" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BW139" t="n">
+        <v>0.3429</v>
+      </c>
+      <c r="BX139" t="n">
+        <v>0.36867</v>
+      </c>
+      <c r="BY139" t="n">
+        <v>0.40635</v>
+      </c>
+      <c r="BZ139" t="n">
+        <v>0.28415</v>
+      </c>
+      <c r="CA139" t="n">
+        <v>0.35447</v>
+      </c>
+      <c r="CB139" t="n">
+        <v>0.31125</v>
+      </c>
+      <c r="CC139" t="n">
+        <v>0.43005</v>
+      </c>
+      <c r="CD139" t="n">
+        <v>0.39597</v>
+      </c>
+      <c r="CE139" t="n">
+        <v>0.34674</v>
+      </c>
+      <c r="CF139" t="n">
+        <v>0.37957</v>
+      </c>
+      <c r="CG139" t="n">
+        <v>0.42474</v>
+      </c>
+      <c r="CH139" t="n">
+        <v>0.70394</v>
+      </c>
+      <c r="CI139" t="n">
+        <v>0.42236</v>
+      </c>
+      <c r="CJ139" t="n">
+        <v>0.40262</v>
+      </c>
+      <c r="CK139" t="n">
+        <v>0.45862</v>
+      </c>
+      <c r="CL139" t="n">
+        <v>0.4005</v>
+      </c>
+      <c r="CM139" t="n">
+        <v>0.38007</v>
+      </c>
+      <c r="CN139" t="n">
+        <v>0.36358</v>
+      </c>
+      <c r="CO139" t="n">
+        <v>0.34557</v>
+      </c>
+      <c r="CP139" t="n">
+        <v>0.32515</v>
+      </c>
+      <c r="CQ139" t="n">
+        <v>0.3727200000000001</v>
+      </c>
+      <c r="CR139" t="n">
+        <v>0.36419</v>
+      </c>
+      <c r="CS139" t="n">
+        <v>0.36875</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="2" t="n">
+        <v>46163</v>
+      </c>
+      <c r="B140" t="n">
+        <v>0.34704</v>
+      </c>
+      <c r="C140" t="n">
+        <v>0.44605</v>
+      </c>
+      <c r="D140" t="n">
+        <v>0.40099</v>
+      </c>
+      <c r="E140" t="n">
+        <v>0.40104</v>
+      </c>
+      <c r="F140" t="n">
+        <v>0.39162</v>
+      </c>
+      <c r="G140" t="n">
+        <v>0.38077</v>
+      </c>
+      <c r="H140" t="n">
+        <v>0.36016</v>
+      </c>
+      <c r="I140" t="n">
+        <v>0.3756</v>
+      </c>
+      <c r="J140" t="n">
+        <v>0.37448</v>
+      </c>
+      <c r="K140" t="n">
+        <v>0.37867</v>
+      </c>
+      <c r="L140" t="n">
+        <v>0.37738</v>
+      </c>
+      <c r="M140" t="n">
+        <v>0.36921</v>
+      </c>
+      <c r="N140" t="n">
+        <v>0.36695</v>
+      </c>
+      <c r="O140" t="n">
+        <v>0.36157</v>
+      </c>
+      <c r="P140" t="n">
+        <v>0.36005</v>
+      </c>
+      <c r="Q140" t="n">
+        <v>0.35981</v>
+      </c>
+      <c r="R140" t="n">
+        <v>0.36041</v>
+      </c>
+      <c r="S140" t="n">
+        <v>0.3559</v>
+      </c>
+      <c r="T140" t="n">
+        <v>0.32893</v>
+      </c>
+      <c r="U140" t="n">
+        <v>0.35619</v>
+      </c>
+      <c r="V140" t="n">
+        <v>0.35112</v>
+      </c>
+      <c r="W140" t="n">
+        <v>0.34992</v>
+      </c>
+      <c r="X140" t="n">
+        <v>0.34724</v>
+      </c>
+      <c r="Y140" t="n">
+        <v>0.35017</v>
+      </c>
+      <c r="Z140" t="n">
+        <v>0.36021</v>
+      </c>
+      <c r="AA140" t="n">
+        <v>0.37109</v>
+      </c>
+      <c r="AB140" t="n">
+        <v>0.3997</v>
+      </c>
+      <c r="AC140" t="n">
+        <v>0.37584</v>
+      </c>
+      <c r="AD140" t="n">
+        <v>0.3696</v>
+      </c>
+      <c r="AE140" t="n">
+        <v>0.31857</v>
+      </c>
+      <c r="AF140" t="n">
+        <v>0.28039</v>
+      </c>
+      <c r="AG140" t="n">
+        <v>0.08153000000000001</v>
+      </c>
+      <c r="AH140" t="n">
+        <v>0.27561</v>
+      </c>
+      <c r="AI140" t="n">
+        <v>0.01701</v>
+      </c>
+      <c r="AJ140" t="n">
+        <v>-0.04224</v>
+      </c>
+      <c r="AK140" t="n">
+        <v>0.01313</v>
+      </c>
+      <c r="AL140" t="n">
+        <v>0.02083</v>
+      </c>
+      <c r="AM140" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AN140" t="n">
+        <v>-0.03322</v>
+      </c>
+      <c r="AO140" t="n">
+        <v>0.32464</v>
+      </c>
+      <c r="AP140" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AQ140" t="n">
+        <v>0.2864</v>
+      </c>
+      <c r="AR140" t="n">
+        <v>0.09684000000000001</v>
+      </c>
+      <c r="AS140" t="n">
+        <v>0.30586</v>
+      </c>
+      <c r="AT140" t="n">
+        <v>0.17605</v>
+      </c>
+      <c r="AU140" t="n">
+        <v>0.3129</v>
+      </c>
+      <c r="AV140" t="n">
+        <v>0.29597</v>
+      </c>
+      <c r="AW140" t="n">
+        <v>0.29631</v>
+      </c>
+      <c r="AX140" t="n">
+        <v>0.29336</v>
+      </c>
+      <c r="AY140" t="n">
+        <v>0.26399</v>
+      </c>
+      <c r="AZ140" t="n">
+        <v>0.28192</v>
+      </c>
+      <c r="BA140" t="n">
+        <v>0.27459</v>
+      </c>
+      <c r="BB140" t="n">
+        <v>0.16098</v>
+      </c>
+      <c r="BC140" t="n">
+        <v>0.31971</v>
+      </c>
+      <c r="BD140" t="n">
+        <v>0.33841</v>
+      </c>
+      <c r="BE140" t="n">
+        <v>0.31086</v>
+      </c>
+      <c r="BF140" t="n">
+        <v>0.15288</v>
+      </c>
+      <c r="BG140" t="n">
+        <v>0.18939</v>
+      </c>
+      <c r="BH140" t="n">
+        <v>0.01257</v>
+      </c>
+      <c r="BI140" t="n">
+        <v>0.0713</v>
+      </c>
+      <c r="BJ140" t="n">
+        <v>0.30239</v>
+      </c>
+      <c r="BK140" t="n">
+        <v>0.27211</v>
+      </c>
+      <c r="BL140" t="n">
+        <v>0.27542</v>
+      </c>
+      <c r="BM140" t="n">
+        <v>0.31751</v>
+      </c>
+      <c r="BN140" t="n">
+        <v>0.29554</v>
+      </c>
+      <c r="BO140" t="n">
+        <v>0.32158</v>
+      </c>
+      <c r="BP140" t="n">
+        <v>0.30347</v>
+      </c>
+      <c r="BQ140" t="n">
+        <v>0.33583</v>
+      </c>
+      <c r="BR140" t="n">
+        <v>0.40102</v>
+      </c>
+      <c r="BS140" t="n">
+        <v>0.32517</v>
+      </c>
+      <c r="BT140" t="n">
+        <v>0.37665</v>
+      </c>
+      <c r="BU140" t="n">
+        <v>0.35866</v>
+      </c>
+      <c r="BV140" t="n">
+        <v>0.36309</v>
+      </c>
+      <c r="BW140" t="n">
+        <v>0.43774</v>
+      </c>
+      <c r="BX140" t="n">
+        <v>0.5327000000000001</v>
+      </c>
+      <c r="BY140" t="n">
+        <v>0.5280199999999999</v>
+      </c>
+      <c r="BZ140" t="n">
+        <v>0.35125</v>
+      </c>
+      <c r="CA140" t="n">
+        <v>0.46189</v>
+      </c>
+      <c r="CB140" t="n">
+        <v>0.5521699999999999</v>
+      </c>
+      <c r="CC140" t="n">
+        <v>0.43568</v>
+      </c>
+      <c r="CD140" t="n">
+        <v>0.30849</v>
+      </c>
+      <c r="CE140" t="n">
+        <v>0.44834</v>
+      </c>
+      <c r="CF140" t="n">
+        <v>0.35525</v>
+      </c>
+      <c r="CG140" t="n">
+        <v>0.5013299999999999</v>
+      </c>
+      <c r="CH140" t="n">
+        <v>0.48246</v>
+      </c>
+      <c r="CI140" t="n">
+        <v>0.71201</v>
+      </c>
+      <c r="CJ140" t="n">
+        <v>0.75261</v>
+      </c>
+      <c r="CK140" t="n">
+        <v>0.5213</v>
+      </c>
+      <c r="CL140" t="n">
+        <v>0.52318</v>
+      </c>
+      <c r="CM140" t="n">
+        <v>0.39838</v>
+      </c>
+      <c r="CN140" t="n">
+        <v>0.44152</v>
+      </c>
+      <c r="CO140" t="n">
+        <v>0.37085</v>
+      </c>
+      <c r="CP140" t="n">
+        <v>0.37241</v>
+      </c>
+      <c r="CQ140" t="n">
+        <v>0.37933</v>
+      </c>
+      <c r="CR140" t="n">
+        <v>0.36961</v>
+      </c>
+      <c r="CS140" t="n">
+        <v>0.37523</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="2" t="n">
+        <v>46164</v>
+      </c>
+      <c r="B141" t="n">
+        <v>0.27134</v>
+      </c>
+      <c r="C141" t="n">
+        <v>0.36987</v>
+      </c>
+      <c r="D141" t="n">
+        <v>0.3196</v>
+      </c>
+      <c r="E141" t="n">
+        <v>0.37068</v>
+      </c>
+      <c r="F141" t="n">
+        <v>0.33479</v>
+      </c>
+      <c r="G141" t="n">
+        <v>0.33774</v>
+      </c>
+      <c r="H141" t="n">
+        <v>0.35013</v>
+      </c>
+      <c r="I141" t="n">
+        <v>0.32114</v>
+      </c>
+      <c r="J141" t="n">
+        <v>0.33479</v>
+      </c>
+      <c r="K141" t="n">
+        <v>0.34182</v>
+      </c>
+      <c r="L141" t="n">
+        <v>0.3386</v>
+      </c>
+      <c r="M141" t="n">
+        <v>0.33927</v>
+      </c>
+      <c r="N141" t="n">
+        <v>0.34593</v>
+      </c>
+      <c r="O141" t="n">
+        <v>0.33567</v>
+      </c>
+      <c r="P141" t="n">
+        <v>0.33772</v>
+      </c>
+      <c r="Q141" t="n">
+        <v>0.33629</v>
+      </c>
+      <c r="R141" t="n">
+        <v>0.31361</v>
+      </c>
+      <c r="S141" t="n">
+        <v>0.32689</v>
+      </c>
+      <c r="T141" t="n">
+        <v>0.31949</v>
+      </c>
+      <c r="U141" t="n">
+        <v>0.31006</v>
+      </c>
+      <c r="V141" t="n">
+        <v>0.30552</v>
+      </c>
+      <c r="W141" t="n">
+        <v>0.30949</v>
+      </c>
+      <c r="X141" t="n">
+        <v>0.30986</v>
+      </c>
+      <c r="Y141" t="n">
+        <v>0.29329</v>
+      </c>
+      <c r="Z141" t="n">
+        <v>0.29314</v>
+      </c>
+      <c r="AA141" t="n">
+        <v>0.34546</v>
+      </c>
+      <c r="AB141" t="n">
+        <v>0.3634</v>
+      </c>
+      <c r="AC141" t="n">
+        <v>0.3057</v>
+      </c>
+      <c r="AD141" t="n">
+        <v>0.29207</v>
+      </c>
+      <c r="AE141" t="n">
+        <v>0.28733</v>
+      </c>
+      <c r="AF141" t="n">
+        <v>0.2814</v>
+      </c>
+      <c r="AG141" t="n">
+        <v>0.27547</v>
+      </c>
+      <c r="AH141" t="n">
+        <v>0.31554</v>
+      </c>
+      <c r="AI141" t="n">
+        <v>0.26243</v>
+      </c>
+      <c r="AJ141" t="n">
+        <v>0.26465</v>
+      </c>
+      <c r="AK141" t="n">
+        <v>0.27903</v>
+      </c>
+      <c r="AL141" t="n">
+        <v>0.20983</v>
+      </c>
+      <c r="AM141" t="n">
+        <v>0.2357</v>
+      </c>
+      <c r="AN141" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AO141" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AP141" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AQ141" t="n">
+        <v>0.13899</v>
+      </c>
+      <c r="AR141" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AS141" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AT141" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AU141" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AV141" t="n">
+        <v>-0.00747</v>
+      </c>
+      <c r="AW141" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AX141" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY141" t="n">
+        <v>-0.02065</v>
+      </c>
+      <c r="AZ141" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BA141" t="n">
+        <v>0.24534</v>
+      </c>
+      <c r="BB141" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BC141" t="n">
+        <v>0.02524</v>
+      </c>
+      <c r="BD141" t="n">
+        <v>0.03624</v>
+      </c>
+      <c r="BE141" t="n">
+        <v>0.03048</v>
+      </c>
+      <c r="BF141" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BG141" t="n">
+        <v>0.01497</v>
+      </c>
+      <c r="BH141" t="n">
+        <v>0.00024</v>
+      </c>
+      <c r="BI141" t="n">
+        <v>0.1264</v>
+      </c>
+      <c r="BJ141" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BK141" t="n">
+        <v>0.11661</v>
+      </c>
+      <c r="BL141" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BM141" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BN141" t="n">
+        <v>0.21291</v>
+      </c>
+      <c r="BO141" t="n">
+        <v>0.19003</v>
+      </c>
+      <c r="BP141" t="n">
+        <v>0.11488</v>
+      </c>
+      <c r="BQ141" t="n">
+        <v>0.33025</v>
+      </c>
+      <c r="BR141" t="n">
+        <v>0.24684</v>
+      </c>
+      <c r="BS141" t="n">
+        <v>0.24247</v>
+      </c>
+      <c r="BT141" t="n">
+        <v>0.30308</v>
+      </c>
+      <c r="BU141" t="n">
+        <v>0.34501</v>
+      </c>
+      <c r="BV141" t="n">
+        <v>0.2253</v>
+      </c>
+      <c r="BW141" t="n">
+        <v>0.32646</v>
+      </c>
+      <c r="BX141" t="n">
+        <v>0.33711</v>
+      </c>
+      <c r="BY141" t="n">
+        <v>0.34743</v>
+      </c>
+      <c r="BZ141" t="n">
+        <v>0.29426</v>
+      </c>
+      <c r="CA141" t="n">
+        <v>0.3767</v>
+      </c>
+      <c r="CB141" t="n">
+        <v>0.39605</v>
+      </c>
+      <c r="CC141" t="n">
+        <v>0.30898</v>
+      </c>
+      <c r="CD141" t="n">
+        <v>0.37741</v>
+      </c>
+      <c r="CE141" t="n">
+        <v>0.30042</v>
+      </c>
+      <c r="CF141" t="n">
+        <v>0.39606</v>
+      </c>
+      <c r="CG141" t="n">
+        <v>0.3772799999999999</v>
+      </c>
+      <c r="CH141" t="n">
+        <v>0.378</v>
+      </c>
+      <c r="CI141" t="n">
+        <v>0.40351</v>
+      </c>
+      <c r="CJ141" t="n">
+        <v>0.38277</v>
+      </c>
+      <c r="CK141" t="n">
+        <v>0.3639</v>
+      </c>
+      <c r="CL141" t="n">
+        <v>0.2805</v>
+      </c>
+      <c r="CM141" t="n">
+        <v>0.32584</v>
+      </c>
+      <c r="CN141" t="n">
+        <v>0.38911</v>
+      </c>
+      <c r="CO141" t="n">
+        <v>0.35782</v>
+      </c>
+      <c r="CP141" t="n">
+        <v>0.35796</v>
+      </c>
+      <c r="CQ141" t="n">
+        <v>0.37361</v>
+      </c>
+      <c r="CR141" t="n">
+        <v>0.38094</v>
+      </c>
+      <c r="CS141" t="n">
+        <v>0.37611</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="2" t="n">
+        <v>46165</v>
+      </c>
+      <c r="B142" t="n">
+        <v>0.35093</v>
+      </c>
+      <c r="C142" t="n">
+        <v>0.77183</v>
+      </c>
+      <c r="D142" t="n">
+        <v>0.3443</v>
+      </c>
+      <c r="E142" t="n">
+        <v>0.40765</v>
+      </c>
+      <c r="F142" t="n">
+        <v>0.38064</v>
+      </c>
+      <c r="G142" t="n">
+        <v>0.34252</v>
+      </c>
+      <c r="H142" t="n">
+        <v>0.33765</v>
+      </c>
+      <c r="I142" t="n">
+        <v>0.35686</v>
+      </c>
+      <c r="J142" t="n">
+        <v>0.35606</v>
+      </c>
+      <c r="K142" t="n">
+        <v>0.38229</v>
+      </c>
+      <c r="L142" t="n">
+        <v>0.34593</v>
+      </c>
+      <c r="M142" t="n">
+        <v>0.34787</v>
+      </c>
+      <c r="N142" t="n">
+        <v>0.34243</v>
+      </c>
+      <c r="O142" t="n">
+        <v>0.37974</v>
+      </c>
+      <c r="P142" t="n">
+        <v>0.35465</v>
+      </c>
+      <c r="Q142" t="n">
+        <v>0.36056</v>
+      </c>
+      <c r="R142" t="n">
+        <v>0.37941</v>
+      </c>
+      <c r="S142" t="n">
+        <v>0.37994</v>
+      </c>
+      <c r="T142" t="n">
+        <v>0.34884</v>
+      </c>
+      <c r="U142" t="n">
+        <v>0.35969</v>
+      </c>
+      <c r="V142" t="n">
+        <v>0.3633</v>
+      </c>
+      <c r="W142" t="n">
+        <v>0.3609</v>
+      </c>
+      <c r="X142" t="n">
+        <v>0.36423</v>
+      </c>
+      <c r="Y142" t="n">
+        <v>0.35595</v>
+      </c>
+      <c r="Z142" t="n">
+        <v>0.36591</v>
+      </c>
+      <c r="AA142" t="n">
+        <v>0.35107</v>
+      </c>
+      <c r="AB142" t="n">
+        <v>0.35102</v>
+      </c>
+      <c r="AC142" t="n">
+        <v>0.34007</v>
+      </c>
+      <c r="AD142" t="n">
+        <v>0.32345</v>
+      </c>
+      <c r="AE142" t="n">
+        <v>0.3244</v>
+      </c>
+      <c r="AF142" t="n">
+        <v>0.30275</v>
+      </c>
+      <c r="AG142" t="n">
+        <v>0.30486</v>
+      </c>
+      <c r="AH142" t="n">
+        <v>0.29722</v>
+      </c>
+      <c r="AI142" t="n">
+        <v>0.27118</v>
+      </c>
+      <c r="AJ142" t="n">
+        <v>0.24409</v>
+      </c>
+      <c r="AK142" t="n">
+        <v>0.22256</v>
+      </c>
+      <c r="AL142" t="n">
+        <v>0.21329</v>
+      </c>
+      <c r="AM142" t="n">
+        <v>0.18308</v>
+      </c>
+      <c r="AN142" t="n">
+        <v>0.18195</v>
+      </c>
+      <c r="AO142" t="n">
+        <v>0.18819</v>
+      </c>
+      <c r="AP142" t="n">
+        <v>0.24001</v>
+      </c>
+      <c r="AQ142" t="n">
+        <v>0.07071</v>
+      </c>
+      <c r="AR142" t="n">
+        <v>-0.01002</v>
+      </c>
+      <c r="AS142" t="n">
+        <v>-0.01918</v>
+      </c>
+      <c r="AT142" t="n">
+        <v>-0.0183</v>
+      </c>
+      <c r="AU142" t="n">
+        <v>0.01631</v>
+      </c>
+      <c r="AV142" t="n">
+        <v>0.09162999999999999</v>
+      </c>
+      <c r="AW142" t="n">
+        <v>0.01772</v>
+      </c>
+      <c r="AX142" t="n">
+        <v>-0.0302</v>
+      </c>
+      <c r="AY142" t="n">
+        <v>0.02017</v>
+      </c>
+      <c r="AZ142" t="n">
+        <v>-0.03253</v>
+      </c>
+      <c r="BA142" t="n">
+        <v>-0.04105</v>
+      </c>
+      <c r="BB142" t="n">
+        <v>-0.02601</v>
+      </c>
+      <c r="BC142" t="n">
+        <v>0.03515</v>
+      </c>
+      <c r="BD142" t="n">
+        <v>-0.03994</v>
+      </c>
+      <c r="BE142" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BF142" t="n">
+        <v>-0.02115</v>
+      </c>
+      <c r="BG142" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BH142" t="n">
+        <v>0.13408</v>
+      </c>
+      <c r="BI142" t="n">
+        <v>-0.0143</v>
+      </c>
+      <c r="BJ142" t="n">
+        <v>0.14981</v>
+      </c>
+      <c r="BK142" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BL142" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BM142" t="n">
+        <v>0.16936</v>
+      </c>
+      <c r="BN142" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BO142" t="n">
+        <v>0.21067</v>
+      </c>
+      <c r="BP142" t="n">
+        <v>0.35141</v>
+      </c>
+      <c r="BQ142" t="n">
+        <v>-0.02634</v>
+      </c>
+      <c r="BR142" t="n">
+        <v>0.0005600000000000001</v>
+      </c>
+      <c r="BS142" t="n">
+        <v>-0.00679</v>
+      </c>
+      <c r="BT142" t="n">
+        <v>0.06570000000000001</v>
+      </c>
+      <c r="BU142" t="n">
+        <v>0.34084</v>
+      </c>
+      <c r="BV142" t="n">
+        <v>0.35757</v>
+      </c>
+      <c r="BW142" t="n">
+        <v>0.45519</v>
+      </c>
+      <c r="BX142" t="n">
+        <v>0.47199</v>
+      </c>
+      <c r="BY142" t="n">
+        <v>0.33236</v>
+      </c>
+      <c r="BZ142" t="n">
+        <v>0.42977</v>
+      </c>
+      <c r="CA142" t="n">
+        <v>0.35897</v>
+      </c>
+      <c r="CB142" t="n">
+        <v>0.53363</v>
+      </c>
+      <c r="CC142" t="n">
+        <v>0.38806</v>
+      </c>
+      <c r="CD142" t="n">
+        <v>0.36521</v>
+      </c>
+      <c r="CE142" t="n">
+        <v>0.46181</v>
+      </c>
+      <c r="CF142" t="n">
+        <v>0.39969</v>
+      </c>
+      <c r="CG142" t="n">
+        <v>0.39674</v>
+      </c>
+      <c r="CH142" t="n">
+        <v>0.39762</v>
+      </c>
+      <c r="CI142" t="n">
+        <v>0.41655</v>
+      </c>
+      <c r="CJ142" t="n">
+        <v>0.32897</v>
+      </c>
+      <c r="CK142" t="n">
+        <v>0.36439</v>
+      </c>
+      <c r="CL142" t="n">
+        <v>0.44182</v>
+      </c>
+      <c r="CM142" t="n">
+        <v>0.35448</v>
+      </c>
+      <c r="CN142" t="n">
+        <v>0.39836</v>
+      </c>
+      <c r="CO142" t="n">
+        <v>0.40109</v>
+      </c>
+      <c r="CP142" t="n">
+        <v>0.38875</v>
+      </c>
+      <c r="CQ142" t="n">
+        <v>0.37721</v>
+      </c>
+      <c r="CR142" t="n">
+        <v>0.37081</v>
+      </c>
+      <c r="CS142" t="n">
+        <v>0.3903</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="2" t="n">
+        <v>46166</v>
+      </c>
+      <c r="B143" t="n">
+        <v>0.32989</v>
+      </c>
+      <c r="C143" t="n">
+        <v>0.50234</v>
+      </c>
+      <c r="D143" t="n">
+        <v>0.40108</v>
+      </c>
+      <c r="E143" t="n">
+        <v>0.40425</v>
+      </c>
+      <c r="F143" t="n">
+        <v>0.31928</v>
+      </c>
+      <c r="G143" t="n">
+        <v>0.37335</v>
+      </c>
+      <c r="H143" t="n">
+        <v>0.36261</v>
+      </c>
+      <c r="I143" t="n">
+        <v>0.36906</v>
+      </c>
+      <c r="J143" t="n">
+        <v>0.35007</v>
+      </c>
+      <c r="K143" t="n">
+        <v>0.41956</v>
+      </c>
+      <c r="L143" t="n">
+        <v>0.34815</v>
+      </c>
+      <c r="M143" t="n">
+        <v>0.37877</v>
+      </c>
+      <c r="N143" t="n">
+        <v>0.37323</v>
+      </c>
+      <c r="O143" t="n">
+        <v>0.34448</v>
+      </c>
+      <c r="P143" t="n">
+        <v>0.34312</v>
+      </c>
+      <c r="Q143" t="n">
+        <v>0.34996</v>
+      </c>
+      <c r="R143" t="n">
+        <v>0.33335</v>
+      </c>
+      <c r="S143" t="n">
+        <v>0.31747</v>
+      </c>
+      <c r="T143" t="n">
+        <v>0.35024</v>
+      </c>
+      <c r="U143" t="n">
+        <v>0.32336</v>
+      </c>
+      <c r="V143" t="n">
+        <v>0.32083</v>
+      </c>
+      <c r="W143" t="n">
+        <v>0.33303</v>
+      </c>
+      <c r="X143" t="n">
+        <v>0.36451</v>
+      </c>
+      <c r="Y143" t="n">
+        <v>0.34043</v>
+      </c>
+      <c r="Z143" t="n">
+        <v>0.35549</v>
+      </c>
+      <c r="AA143" t="n">
+        <v>0.34169</v>
+      </c>
+      <c r="AB143" t="n">
+        <v>0.34971</v>
+      </c>
+      <c r="AC143" t="n">
+        <v>0.34219</v>
+      </c>
+      <c r="AD143" t="n">
+        <v>0.32472</v>
+      </c>
+      <c r="AE143" t="n">
+        <v>0.2949</v>
+      </c>
+      <c r="AF143" t="n">
+        <v>0.25819</v>
+      </c>
+      <c r="AG143" t="n">
+        <v>0.22296</v>
+      </c>
+      <c r="AH143" t="n">
+        <v>0.20364</v>
+      </c>
+      <c r="AI143" t="n">
+        <v>0.13469</v>
+      </c>
+      <c r="AJ143" t="n">
+        <v>0.18202</v>
+      </c>
+      <c r="AK143" t="n">
+        <v>0.22049</v>
+      </c>
+      <c r="AL143" t="n">
+        <v>0.20821</v>
+      </c>
+      <c r="AM143" t="n">
+        <v>0.12866</v>
+      </c>
+      <c r="AN143" t="n">
+        <v>0.1402</v>
+      </c>
+      <c r="AO143" t="n">
+        <v>0.02352</v>
+      </c>
+      <c r="AP143" t="n">
+        <v>0.11088</v>
+      </c>
+      <c r="AQ143" t="n">
+        <v>-0.0362</v>
+      </c>
+      <c r="AR143" t="n">
+        <v>-0.03917</v>
+      </c>
+      <c r="AS143" t="n">
+        <v>-0.0403</v>
+      </c>
+      <c r="AT143" t="n">
+        <v>-0.04182</v>
+      </c>
+      <c r="AU143" t="n">
+        <v>-0.03222999999999999</v>
+      </c>
+      <c r="AV143" t="n">
+        <v>0.009949999999999999</v>
+      </c>
+      <c r="AW143" t="n">
+        <v>-0.04319</v>
+      </c>
+      <c r="AX143" t="n">
+        <v>0.03444</v>
+      </c>
+      <c r="AY143" t="n">
+        <v>-0.02543</v>
+      </c>
+      <c r="AZ143" t="n">
+        <v>-0.03485</v>
+      </c>
+      <c r="BA143" t="n">
+        <v>-0.04295</v>
+      </c>
+      <c r="BB143" t="n">
+        <v>0.07958</v>
+      </c>
+      <c r="BC143" t="n">
+        <v>-0.04172</v>
+      </c>
+      <c r="BD143" t="n">
+        <v>-0.0448</v>
+      </c>
+      <c r="BE143" t="n">
+        <v>-0.04232</v>
+      </c>
+      <c r="BF143" t="n">
+        <v>-0.03445</v>
+      </c>
+      <c r="BG143" t="n">
+        <v>-0.04063</v>
+      </c>
+      <c r="BH143" t="n">
+        <v>-0.04298</v>
+      </c>
+      <c r="BI143" t="n">
+        <v>-0.03439</v>
+      </c>
+      <c r="BJ143" t="n">
+        <v>-0.02619</v>
+      </c>
+      <c r="BK143" t="n">
+        <v>-0.03829</v>
+      </c>
+      <c r="BL143" t="n">
+        <v>-0.03811</v>
+      </c>
+      <c r="BM143" t="n">
+        <v>-0.02467</v>
+      </c>
+      <c r="BN143" t="n">
+        <v>-0.02842</v>
+      </c>
+      <c r="BO143" t="n">
+        <v>0.18328</v>
+      </c>
+      <c r="BP143" t="n">
+        <v>0.21655</v>
+      </c>
+      <c r="BQ143" t="n">
+        <v>0.23819</v>
+      </c>
+      <c r="BR143" t="n">
+        <v>0.24313</v>
+      </c>
+      <c r="BS143" t="n">
+        <v>0.2499</v>
+      </c>
+      <c r="BT143" t="n">
+        <v>0.26554</v>
+      </c>
+      <c r="BU143" t="n">
+        <v>0.27144</v>
+      </c>
+      <c r="BV143" t="n">
+        <v>0.2731</v>
+      </c>
+      <c r="BW143" t="n">
+        <v>0.30498</v>
+      </c>
+      <c r="BX143" t="n">
+        <v>0.36696</v>
+      </c>
+      <c r="BY143" t="n">
+        <v>0.39936</v>
+      </c>
+      <c r="BZ143" t="n">
+        <v>0.33206</v>
+      </c>
+      <c r="CA143" t="n">
+        <v>0.31951</v>
+      </c>
+      <c r="CB143" t="n">
+        <v>0.29084</v>
+      </c>
+      <c r="CC143" t="n">
+        <v>0.35393</v>
+      </c>
+      <c r="CD143" t="n">
+        <v>0.36392</v>
+      </c>
+      <c r="CE143" t="n">
+        <v>0.37952</v>
+      </c>
+      <c r="CF143" t="n">
+        <v>0.35857</v>
+      </c>
+      <c r="CG143" t="n">
+        <v>0.35435</v>
+      </c>
+      <c r="CH143" t="n">
+        <v>0.38432</v>
+      </c>
+      <c r="CI143" t="n">
+        <v>0.40909</v>
+      </c>
+      <c r="CJ143" t="n">
+        <v>0.39169</v>
+      </c>
+      <c r="CK143" t="n">
+        <v>0.48221</v>
+      </c>
+      <c r="CL143" t="n">
+        <v>0.3897</v>
+      </c>
+      <c r="CM143" t="n">
+        <v>0.41885</v>
+      </c>
+      <c r="CN143" t="n">
+        <v>0.43443</v>
+      </c>
+      <c r="CO143" t="n">
+        <v>0.41343</v>
+      </c>
+      <c r="CP143" t="n">
+        <v>0.39485</v>
+      </c>
+      <c r="CQ143" t="n">
+        <v>0.40872</v>
+      </c>
+      <c r="CR143" t="n">
+        <v>0.40983</v>
+      </c>
+      <c r="CS143" t="n">
+        <v>0.38401</v>
       </c>
     </row>
   </sheetData>
